--- a/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,86 +434,2548 @@
           <t>copiado_formaciones</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.99671717171717</v>
+      </c>
+      <c r="D2" t="n">
+        <v>184.6834595959596</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.206060606060606</v>
+      </c>
+      <c r="F2" t="n">
+        <v>79.97651515151514</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29083459.5959596</v>
+      </c>
+      <c r="H2" t="n">
+        <v>84.28800505050505</v>
+      </c>
+      <c r="I2" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="J2" t="n">
+        <v>183.7090909090909</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.538181818181818</v>
+      </c>
+      <c r="L2" t="n">
+        <v>77.04545454545455</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12758545.45454545</v>
+      </c>
+      <c r="N2" t="n">
+        <v>78.86363636363636</v>
+      </c>
+      <c r="O2" t="n">
+        <v>24.25017586580087</v>
+      </c>
+      <c r="P2" t="n">
+        <v>184.4930194805195</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.762959956709957</v>
+      </c>
+      <c r="R2" t="n">
+        <v>74.79669462481962</v>
+      </c>
+      <c r="S2" t="n">
+        <v>18135945.27867965</v>
+      </c>
+      <c r="T2" t="n">
+        <v>81.31994047619048</v>
+      </c>
+      <c r="U2" t="n">
+        <v>28.05752344416027</v>
+      </c>
+      <c r="V2" t="n">
+        <v>181.6255242966752</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.267855924978687</v>
+      </c>
+      <c r="X2" t="n">
+        <v>74.90514492753623</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6900034.52685422</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>76.2950895140665</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="D3" t="n">
+        <v>182.5454545454546</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2733333.333333333</v>
+      </c>
+      <c r="H3" t="n">
+        <v>74.39393939393939</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.91666666666667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>182.9530303030303</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.703030303030303</v>
+      </c>
+      <c r="L3" t="n">
+        <v>83.27878787878787</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49500454.54545454</v>
+      </c>
+      <c r="N3" t="n">
+        <v>85.84090909090908</v>
+      </c>
+      <c r="O3" t="n">
+        <v>25.48611111111111</v>
+      </c>
+      <c r="P3" t="n">
+        <v>184.0714285714286</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>69.23214285714285</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2203174.603174603</v>
+      </c>
+      <c r="T3" t="n">
+        <v>73.69047619047619</v>
+      </c>
+      <c r="U3" t="n">
+        <v>23.63634403036577</v>
+      </c>
+      <c r="V3" t="n">
+        <v>184.0894151138716</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.92542270531401</v>
+      </c>
+      <c r="X3" t="n">
+        <v>80.0898464458247</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>35575754.83091787</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>84.65126811594202</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24.28472222222222</v>
+      </c>
+      <c r="D4" t="n">
+        <v>183.4837962962963</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.24537037037037</v>
+      </c>
+      <c r="F4" t="n">
+        <v>83.53472222222221</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60335648.14814815</v>
+      </c>
+      <c r="H4" t="n">
+        <v>86.53472222222221</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25.86111111111111</v>
+      </c>
+      <c r="J4" t="n">
+        <v>182.7685185185185</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.400462962962963</v>
+      </c>
+      <c r="L4" t="n">
+        <v>76.31018518518518</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12360706.01851852</v>
+      </c>
+      <c r="N4" t="n">
+        <v>79.67824074074075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24.66080977845684</v>
+      </c>
+      <c r="P4" t="n">
+        <v>179.023548175251</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.799314462627156</v>
+      </c>
+      <c r="R4" t="n">
+        <v>81.23983086057389</v>
+      </c>
+      <c r="S4" t="n">
+        <v>37182685.99305751</v>
+      </c>
+      <c r="T4" t="n">
+        <v>84.51666934716469</v>
+      </c>
+      <c r="U4" t="n">
+        <v>24.5508658008658</v>
+      </c>
+      <c r="V4" t="n">
+        <v>180.5383572567783</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.323638642059695</v>
+      </c>
+      <c r="X4" t="n">
+        <v>72.51085668717248</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8506428.001822738</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>78.65628844839371</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>hdlcFVpd</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27.36363636363636</v>
+      </c>
+      <c r="D5" t="n">
+        <v>183.3484848484849</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.606060606060606</v>
+      </c>
+      <c r="F5" t="n">
+        <v>76.59090909090911</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10924621.21212121</v>
+      </c>
+      <c r="H5" t="n">
+        <v>79.04545454545455</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.93111111111111</v>
+      </c>
+      <c r="J5" t="n">
+        <v>181.8622222222222</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L5" t="n">
+        <v>75.38</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8726222.222222222</v>
+      </c>
+      <c r="N5" t="n">
+        <v>79.88444444444445</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24.63790951163074</v>
+      </c>
+      <c r="P5" t="n">
+        <v>186.731731823164</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.361362805991962</v>
+      </c>
+      <c r="R5" t="n">
+        <v>72.57060041407867</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7044595.207648277</v>
+      </c>
+      <c r="T5" t="n">
+        <v>77.17188527584948</v>
+      </c>
+      <c r="U5" t="n">
+        <v>23.06374269005848</v>
+      </c>
+      <c r="V5" t="n">
+        <v>177.9514619883041</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.354093567251462</v>
+      </c>
+      <c r="X5" t="n">
+        <v>72.96871345029238</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7907032.16374269</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>80.36725146198832</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>184.9742424242424</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.506060606060606</v>
+      </c>
+      <c r="F6" t="n">
+        <v>77.72575757575758</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19252575.75757575</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.90454545454544</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.62727272727273</v>
+      </c>
+      <c r="J6" t="n">
+        <v>179.974025974026</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>72.75844155844155</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4395454.545454546</v>
+      </c>
+      <c r="N6" t="n">
+        <v>76.02987012987013</v>
+      </c>
+      <c r="O6" t="n">
+        <v>26.55337301587302</v>
+      </c>
+      <c r="P6" t="n">
+        <v>181.5990079365079</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>75.42678571428571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15324102.18253968</v>
+      </c>
+      <c r="T6" t="n">
+        <v>79.26924603174604</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24.93857543017207</v>
+      </c>
+      <c r="V6" t="n">
+        <v>178.8070158498182</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>70.99022565547958</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3143829.836282339</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>75.32631313394923</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>184.86</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F7" t="n">
+        <v>75.25999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>78.67999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>24.06666666666667</v>
+      </c>
+      <c r="J7" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="L7" t="n">
+        <v>74.89999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8710000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>79.01666666666667</v>
+      </c>
+      <c r="O7" t="n">
+        <v>24.78453416149068</v>
+      </c>
+      <c r="P7" t="n">
+        <v>185.8153830227743</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.430248447204969</v>
+      </c>
+      <c r="R7" t="n">
+        <v>75.23780538302279</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10522339.54451346</v>
+      </c>
+      <c r="T7" t="n">
+        <v>79.59751552795031</v>
+      </c>
+      <c r="U7" t="n">
+        <v>23.88922305764411</v>
+      </c>
+      <c r="V7" t="n">
+        <v>183.0538935723146</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.315946431735905</v>
+      </c>
+      <c r="X7" t="n">
+        <v>74.04833675096833</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10653744.2722969</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>78.96976405660617</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>nHdPI4il</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>28.05454545454545</v>
+      </c>
+      <c r="D8" t="n">
+        <v>183.3272727272727</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.145454545454546</v>
+      </c>
+      <c r="F8" t="n">
+        <v>79</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18487272.72727273</v>
+      </c>
+      <c r="H8" t="n">
+        <v>80.32727272727273</v>
+      </c>
+      <c r="I8" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="J8" t="n">
+        <v>182.0181818181819</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.163636363636364</v>
+      </c>
+      <c r="L8" t="n">
+        <v>79.96363636363637</v>
+      </c>
+      <c r="M8" t="n">
+        <v>26307272.72727273</v>
+      </c>
+      <c r="N8" t="n">
+        <v>81.67272727272727</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26.87345811051694</v>
+      </c>
+      <c r="P8" t="n">
+        <v>180.5931066972244</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.699712248535778</v>
+      </c>
+      <c r="R8" t="n">
+        <v>73.25849503437739</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9518856.760886172</v>
+      </c>
+      <c r="T8" t="n">
+        <v>77.69413547237077</v>
+      </c>
+      <c r="U8" t="n">
+        <v>23.42254901960784</v>
+      </c>
+      <c r="V8" t="n">
+        <v>183.7293300653595</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.603349673202614</v>
+      </c>
+      <c r="X8" t="n">
+        <v>72.96756535947713</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12256787.17320262</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>79.08905228758169</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>8WpYGrM0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>184.6363636363637</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.054545454545454</v>
+      </c>
+      <c r="F9" t="n">
+        <v>76.92727272727272</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12556363.63636364</v>
+      </c>
+      <c r="H9" t="n">
+        <v>79.41818181818181</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="J9" t="n">
+        <v>183.6212121212121</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="L9" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14727272.72727273</v>
+      </c>
+      <c r="N9" t="n">
+        <v>80.25757575757575</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.90455108359133</v>
+      </c>
+      <c r="P9" t="n">
+        <v>181.333653250774</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.094922600619195</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73.53170278637772</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6528724.458204335</v>
+      </c>
+      <c r="T9" t="n">
+        <v>77.56572755417957</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26.49900793650794</v>
+      </c>
+      <c r="V9" t="n">
+        <v>183.9642857142857</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.149140211640212</v>
+      </c>
+      <c r="X9" t="n">
+        <v>73.3558201058201</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8025330.687830688</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>76.56316137566138</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24.99671717171717</v>
+      </c>
+      <c r="D10" t="n">
+        <v>184.6834595959596</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.206060606060606</v>
+      </c>
+      <c r="F10" t="n">
+        <v>79.97651515151514</v>
+      </c>
+      <c r="G10" t="n">
+        <v>29083459.5959596</v>
+      </c>
+      <c r="H10" t="n">
+        <v>84.28800505050505</v>
+      </c>
+      <c r="I10" t="n">
+        <v>27.02045454545454</v>
+      </c>
+      <c r="J10" t="n">
+        <v>182.2965909090909</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.228409090909091</v>
+      </c>
+      <c r="L10" t="n">
+        <v>85.92272727272729</v>
+      </c>
+      <c r="M10" t="n">
+        <v>75244318.18181819</v>
+      </c>
+      <c r="N10" t="n">
+        <v>87.69886363636363</v>
+      </c>
+      <c r="O10" t="n">
+        <v>24.25017586580087</v>
+      </c>
+      <c r="P10" t="n">
+        <v>184.4930194805195</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.762959956709957</v>
+      </c>
+      <c r="R10" t="n">
+        <v>74.79669462481962</v>
+      </c>
+      <c r="S10" t="n">
+        <v>18135945.27867965</v>
+      </c>
+      <c r="T10" t="n">
+        <v>81.31994047619048</v>
+      </c>
+      <c r="U10" t="n">
+        <v>24.74854806052856</v>
+      </c>
+      <c r="V10" t="n">
+        <v>178.5162910272805</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.278723536516056</v>
+      </c>
+      <c r="X10" t="n">
+        <v>80.59222257743677</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>44444087.45382211</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>85.10128498863313</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="J11" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2586111.111111111</v>
+      </c>
+      <c r="N11" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>23.43472222222222</v>
+      </c>
+      <c r="V11" t="n">
+        <v>182.5714285714286</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>68.16527777777777</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2176979.166666667</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>74.02242063492064</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>25.53939393939394</v>
+      </c>
+      <c r="J13" t="n">
+        <v>180.6757575757576</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>70.12121212121212</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2251969.696969697</v>
+      </c>
+      <c r="N13" t="n">
+        <v>73</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>21.44033613445378</v>
+      </c>
+      <c r="V13" t="n">
+        <v>177.9665732959851</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>65.98991596638655</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1754393.090569561</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>75.46479925303454</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23.15277777777778</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>68.45833333333333</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2093981.481481481</v>
+      </c>
+      <c r="H16" t="n">
+        <v>74.58333333333333</v>
+      </c>
+      <c r="I16" t="n">
+        <v>23.91944444444444</v>
+      </c>
+      <c r="J16" t="n">
+        <v>182.2533333333333</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>71.35111111111111</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4265277.777777778</v>
+      </c>
+      <c r="N16" t="n">
+        <v>77.18944444444443</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25.8292663476874</v>
+      </c>
+      <c r="P16" t="n">
+        <v>180.2996810207337</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>67.52958532695375</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1649124.800637959</v>
+      </c>
+      <c r="T16" t="n">
+        <v>72.44808612440193</v>
+      </c>
+      <c r="U16" t="n">
+        <v>24.21920483025746</v>
+      </c>
+      <c r="V16" t="n">
+        <v>181.9104591023012</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>68.69405559352928</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2797111.187058555</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>74.53902654363181</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>182.4666666666667</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="L19" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1895833.333333333</v>
+      </c>
+      <c r="N19" t="n">
+        <v>71.89999999999999</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>26.1699604743083</v>
+      </c>
+      <c r="V19" t="n">
+        <v>180.9741106719368</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>67.64532279314888</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1443914.690382082</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>71.43814229249011</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26</v>
+      </c>
+      <c r="D20" t="n">
+        <v>183.2333333333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>68.89999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>71.83333333333333</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>24.04629629629629</v>
+      </c>
+      <c r="P20" t="n">
+        <v>182.5436507936508</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>63.12169312169313</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1106871.693121693</v>
+      </c>
+      <c r="T20" t="n">
+        <v>68.84656084656085</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>25.03030303030303</v>
+      </c>
+      <c r="J21" t="n">
+        <v>182.2424242424242</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>69.3030303030303</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2061818.181818182</v>
+      </c>
+      <c r="N21" t="n">
+        <v>73.51515151515152</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>26.69074074074074</v>
+      </c>
+      <c r="V21" t="n">
+        <v>178.3407407407407</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>68.0351851851852</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1474120.37037037</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>71.08333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>185.34</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L25" t="n">
+        <v>71.45999999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2426000</v>
+      </c>
+      <c r="N25" t="n">
+        <v>72.86000000000001</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>27.8981884057971</v>
+      </c>
+      <c r="V25" t="n">
+        <v>183.9869565217391</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.094565217391304</v>
+      </c>
+      <c r="X25" t="n">
+        <v>70.8876811594203</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2380326.086956522</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>72.71231884057971</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1638750</v>
+      </c>
+      <c r="H27" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>23.27250712250712</v>
+      </c>
+      <c r="P27" t="n">
+        <v>183.2507122507123</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>65.71353276353275</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1436460.113960114</v>
+      </c>
+      <c r="T27" t="n">
+        <v>73.40313390313391</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>26.22888888888889</v>
+      </c>
+      <c r="D30" t="n">
+        <v>182.6111111111111</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>72.32444444444445</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3313777.777777778</v>
+      </c>
+      <c r="H30" t="n">
+        <v>74.8111111111111</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>25.76604776297871</v>
+      </c>
+      <c r="P30" t="n">
+        <v>183.9617530806789</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>69.36187597568671</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2407644.63413824</v>
+      </c>
+      <c r="T30" t="n">
+        <v>73.22434649749228</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>25.56666666666667</v>
+      </c>
+      <c r="J32" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>69.86666666666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2524166.666666667</v>
+      </c>
+      <c r="N32" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>25.99801587301587</v>
+      </c>
+      <c r="V32" t="n">
+        <v>179.5912698412699</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>68.37103174603175</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1671577.380952381</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>72.96428571428572</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>26.47685185185185</v>
+      </c>
+      <c r="D33" t="n">
+        <v>184.3425925925926</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>70.14814814814814</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2017013.888888889</v>
+      </c>
+      <c r="H33" t="n">
+        <v>72.02314814814814</v>
+      </c>
+      <c r="I33" t="n">
+        <v>22.42962962962963</v>
+      </c>
+      <c r="J33" t="n">
+        <v>182.2111111111111</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>69.18888888888888</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2930185.185185185</v>
+      </c>
+      <c r="N33" t="n">
+        <v>76.78148148148148</v>
+      </c>
+      <c r="O33" t="n">
+        <v>23.61013645224171</v>
+      </c>
+      <c r="P33" t="n">
+        <v>181.3713450292398</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>66.93567251461988</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1723440.545808967</v>
+      </c>
+      <c r="T33" t="n">
+        <v>73.50974658869397</v>
+      </c>
+      <c r="U33" t="n">
+        <v>22.7132857719747</v>
+      </c>
+      <c r="V33" t="n">
+        <v>181.6893256158299</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>66.28680396643783</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1836649.167676224</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>73.81612599273119</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>181.4333333333333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1041666.666666667</v>
+      </c>
+      <c r="H34" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>26.44412393162393</v>
+      </c>
+      <c r="P34" t="n">
+        <v>183.0144230769231</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>65.60854700854701</v>
+      </c>
+      <c r="S34" t="n">
+        <v>958325.3205128206</v>
+      </c>
+      <c r="T34" t="n">
+        <v>69.13215811965811</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>24.20833333333333</v>
+      </c>
+      <c r="D37" t="n">
+        <v>179.7916666666667</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>68.79166666666667</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1970833.333333333</v>
+      </c>
+      <c r="H37" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>24.39869281045752</v>
+      </c>
+      <c r="P37" t="n">
+        <v>180.2530204000792</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>67.35244602891662</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1574286.987522282</v>
+      </c>
+      <c r="T37" t="n">
+        <v>72.71548821548822</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>24.12121212121212</v>
+      </c>
+      <c r="D40" t="n">
+        <v>183.7575757575758</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2534545.454545455</v>
+      </c>
+      <c r="H40" t="n">
+        <v>74.24242424242424</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>23.6031746031746</v>
+      </c>
+      <c r="P40" t="n">
+        <v>181.4146825396825</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>67.31547619047619</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1888819.444444445</v>
+      </c>
+      <c r="T40" t="n">
+        <v>73.60317460317459</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>23.9469696969697</v>
+      </c>
+      <c r="D42" t="n">
+        <v>181.6301346801347</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>71.23400673400674</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3912899.831649832</v>
+      </c>
+      <c r="H42" t="n">
+        <v>77.02205387205389</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>23.05900300966091</v>
+      </c>
+      <c r="P42" t="n">
+        <v>179.9004198530514</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>68.90433348328084</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2854691.814338196</v>
+      </c>
+      <c r="T42" t="n">
+        <v>76.35960587901377</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>24</v>
+      </c>
+      <c r="D43" t="n">
+        <v>179.9090909090909</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="F43" t="n">
+        <v>69.65909090909092</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3025000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>75.06818181818183</v>
+      </c>
+      <c r="I43" t="n">
+        <v>27.16363636363636</v>
+      </c>
+      <c r="J43" t="n">
+        <v>182.0060606060606</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>67.67878787878789</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1262727.272727273</v>
+      </c>
+      <c r="N43" t="n">
+        <v>70.35151515151516</v>
+      </c>
+      <c r="O43" t="n">
+        <v>25.18951914098973</v>
+      </c>
+      <c r="P43" t="n">
+        <v>180.955987394958</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="R43" t="n">
+        <v>70.16818394024276</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2982754.726890756</v>
+      </c>
+      <c r="T43" t="n">
+        <v>74.78092903828198</v>
+      </c>
+      <c r="U43" t="n">
+        <v>25.92451690821256</v>
+      </c>
+      <c r="V43" t="n">
+        <v>185.8272946859903</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>66.48128019323671</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1146784.420289855</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>70.07910628019323</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>24.39393939393939</v>
+      </c>
+      <c r="D44" t="n">
+        <v>181.2424242424242</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>68.24242424242425</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2218939.393939394</v>
+      </c>
+      <c r="H44" t="n">
+        <v>73.93939393939394</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>24</v>
+      </c>
+      <c r="P44" t="n">
+        <v>181.7615942028986</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>66.23985507246377</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1441865.942028986</v>
+      </c>
+      <c r="T44" t="n">
+        <v>72.92318840579711</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>22.85925925925926</v>
+      </c>
+      <c r="D45" t="n">
+        <v>184.7222222222223</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.233333333333333</v>
+      </c>
+      <c r="F45" t="n">
+        <v>74.34074074074074</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8813703.703703703</v>
+      </c>
+      <c r="H45" t="n">
+        <v>80.6962962962963</v>
+      </c>
+      <c r="I45" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>182.2666666666667</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="L45" t="n">
+        <v>69.13333333333334</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2423333.333333333</v>
+      </c>
+      <c r="N45" t="n">
+        <v>75.60000000000001</v>
+      </c>
+      <c r="O45" t="n">
+        <v>24.44442007797271</v>
+      </c>
+      <c r="P45" t="n">
+        <v>179.8515229044834</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.019188596491228</v>
+      </c>
+      <c r="R45" t="n">
+        <v>73.15342348927875</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5622342.83625731</v>
+      </c>
+      <c r="T45" t="n">
+        <v>77.49465155945418</v>
+      </c>
+      <c r="U45" t="n">
+        <v>22.65073099415205</v>
+      </c>
+      <c r="V45" t="n">
+        <v>179.8783625730995</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.017543859649123</v>
+      </c>
+      <c r="X45" t="n">
+        <v>66.61827485380117</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1908505.116959064</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>74.17690058479532</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:Z47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.99671717171717</v>
+        <v>24.68215488215488</v>
       </c>
       <c r="D2" t="n">
-        <v>184.6834595959596</v>
+        <v>184.9391414141414</v>
       </c>
       <c r="E2" t="n">
-        <v>2.206060606060606</v>
+        <v>2.213636363636363</v>
       </c>
       <c r="F2" t="n">
-        <v>79.97651515151514</v>
+        <v>79.82323232323232</v>
       </c>
       <c r="G2" t="n">
-        <v>29083459.5959596</v>
+        <v>29785223.06397307</v>
       </c>
       <c r="H2" t="n">
-        <v>84.28800505050505</v>
+        <v>84.46085858585859</v>
       </c>
       <c r="I2" t="n">
-        <v>27.04</v>
+        <v>26.86969696969697</v>
       </c>
       <c r="J2" t="n">
-        <v>183.7090909090909</v>
+        <v>184.1666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>1.538181818181818</v>
+        <v>1.525252525252525</v>
       </c>
       <c r="L2" t="n">
-        <v>77.04545454545455</v>
+        <v>77.09696969696968</v>
       </c>
       <c r="M2" t="n">
-        <v>12758545.45454545</v>
+        <v>12918585.85858586</v>
       </c>
       <c r="N2" t="n">
-        <v>78.86363636363636</v>
+        <v>79.13232323232323</v>
       </c>
       <c r="O2" t="n">
-        <v>24.25017586580087</v>
+        <v>24.36465025513938</v>
       </c>
       <c r="P2" t="n">
-        <v>184.4930194805195</v>
+        <v>184.0855234540017</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.762959956709957</v>
+        <v>1.862102128949955</v>
       </c>
       <c r="R2" t="n">
-        <v>74.79669462481962</v>
+        <v>75.34181815567685</v>
       </c>
       <c r="S2" t="n">
-        <v>18135945.27867965</v>
+        <v>19042710.4997961</v>
       </c>
       <c r="T2" t="n">
-        <v>81.31994047619048</v>
+        <v>81.57359960892569</v>
       </c>
       <c r="U2" t="n">
-        <v>28.05752344416027</v>
+        <v>28.18738074940121</v>
       </c>
       <c r="V2" t="n">
-        <v>181.6255242966752</v>
+        <v>181.4010849267243</v>
       </c>
       <c r="W2" t="n">
-        <v>1.267855924978687</v>
+        <v>1.306216254617789</v>
       </c>
       <c r="X2" t="n">
-        <v>74.90514492753623</v>
+        <v>74.99756728778468</v>
       </c>
       <c r="Y2" t="n">
-        <v>6900034.52685422</v>
+        <v>6996646.165712661</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.2950895140665</v>
+        <v>76.20626666125388</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.45454545454545</v>
+        <v>26.34090909090909</v>
       </c>
       <c r="D3" t="n">
-        <v>182.5454545454546</v>
+        <v>182.5681818181818</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>71.09090909090909</v>
+        <v>70.88636363636363</v>
       </c>
       <c r="G3" t="n">
-        <v>2733333.333333333</v>
+        <v>2750000</v>
       </c>
       <c r="H3" t="n">
-        <v>74.39393939393939</v>
+        <v>74.39772727272728</v>
       </c>
       <c r="I3" t="n">
-        <v>25.91666666666667</v>
+        <v>25.72272727272728</v>
       </c>
       <c r="J3" t="n">
-        <v>182.9530303030303</v>
+        <v>183.3354545454545</v>
       </c>
       <c r="K3" t="n">
-        <v>2.703030303030303</v>
+        <v>2.621818181818182</v>
       </c>
       <c r="L3" t="n">
-        <v>83.27878787878787</v>
+        <v>82.80363636363636</v>
       </c>
       <c r="M3" t="n">
-        <v>49500454.54545454</v>
+        <v>46842090.90909091</v>
       </c>
       <c r="N3" t="n">
-        <v>85.84090909090908</v>
+        <v>85.60454545454544</v>
       </c>
       <c r="O3" t="n">
-        <v>25.48611111111111</v>
+        <v>25.15104166666667</v>
       </c>
       <c r="P3" t="n">
-        <v>184.0714285714286</v>
+        <v>183.3184523809524</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>69.23214285714285</v>
+        <v>68.9985119047619</v>
       </c>
       <c r="S3" t="n">
-        <v>2203174.603174603</v>
+        <v>2202232.142857143</v>
       </c>
       <c r="T3" t="n">
-        <v>73.69047619047619</v>
+        <v>73.44122023809524</v>
       </c>
       <c r="U3" t="n">
-        <v>23.63634403036577</v>
+        <v>23.29439745463403</v>
       </c>
       <c r="V3" t="n">
-        <v>184.0894151138716</v>
+        <v>183.5194333820485</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92542270531401</v>
+        <v>1.813264827670199</v>
       </c>
       <c r="X3" t="n">
-        <v>80.0898464458247</v>
+        <v>79.55400590671051</v>
       </c>
       <c r="Y3" t="n">
-        <v>35575754.83091787</v>
+        <v>34401151.77810254</v>
       </c>
       <c r="Z3" t="n">
-        <v>84.65126811594202</v>
+        <v>84.53704938497137</v>
       </c>
     </row>
     <row r="4">
@@ -729,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>24.28472222222222</v>
+        <v>24.45416666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>183.4837962962963</v>
+        <v>182.8930555555555</v>
       </c>
       <c r="E4" t="n">
-        <v>2.24537037037037</v>
+        <v>2.236111111111111</v>
       </c>
       <c r="F4" t="n">
-        <v>83.53472222222221</v>
+        <v>83.40416666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>60335648.14814815</v>
+        <v>58345833.33333334</v>
       </c>
       <c r="H4" t="n">
-        <v>86.53472222222221</v>
+        <v>86.30833333333332</v>
       </c>
       <c r="I4" t="n">
-        <v>25.86111111111111</v>
+        <v>26.37962962962963</v>
       </c>
       <c r="J4" t="n">
-        <v>182.7685185185185</v>
+        <v>182.8317901234568</v>
       </c>
       <c r="K4" t="n">
-        <v>1.400462962962963</v>
+        <v>1.447530864197531</v>
       </c>
       <c r="L4" t="n">
-        <v>76.31018518518518</v>
+        <v>76.59567901234567</v>
       </c>
       <c r="M4" t="n">
-        <v>12360706.01851852</v>
+        <v>12223804.01234568</v>
       </c>
       <c r="N4" t="n">
-        <v>79.67824074074075</v>
+        <v>79.56327160493828</v>
       </c>
       <c r="O4" t="n">
-        <v>24.66080977845684</v>
+        <v>24.63040227574283</v>
       </c>
       <c r="P4" t="n">
-        <v>179.023548175251</v>
+        <v>179.6681381930763</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.799314462627156</v>
+        <v>1.772715612560814</v>
       </c>
       <c r="R4" t="n">
-        <v>81.23983086057389</v>
+        <v>81.20040006433194</v>
       </c>
       <c r="S4" t="n">
-        <v>37182685.99305751</v>
+        <v>37424843.79397692</v>
       </c>
       <c r="T4" t="n">
-        <v>84.51666934716469</v>
+        <v>84.53740098910377</v>
       </c>
       <c r="U4" t="n">
-        <v>24.5508658008658</v>
+        <v>23.99087871193134</v>
       </c>
       <c r="V4" t="n">
-        <v>180.5383572567783</v>
+        <v>181.2875089238247</v>
       </c>
       <c r="W4" t="n">
-        <v>1.323638642059695</v>
+        <v>1.278936735778841</v>
       </c>
       <c r="X4" t="n">
-        <v>72.51085668717248</v>
+        <v>71.77806789701526</v>
       </c>
       <c r="Y4" t="n">
-        <v>8506428.001822738</v>
+        <v>8070421.128579023</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.65628844839371</v>
+        <v>78.70129186602871</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27.36363636363636</v>
+        <v>27.2</v>
       </c>
       <c r="D5" t="n">
-        <v>183.3484848484849</v>
+        <v>183.8545454545455</v>
       </c>
       <c r="E5" t="n">
-        <v>1.606060606060606</v>
+        <v>1.581818181818181</v>
       </c>
       <c r="F5" t="n">
-        <v>76.59090909090911</v>
+        <v>76.67272727272727</v>
       </c>
       <c r="G5" t="n">
-        <v>10924621.21212121</v>
+        <v>11300000</v>
       </c>
       <c r="H5" t="n">
-        <v>79.04545454545455</v>
+        <v>79.18181818181817</v>
       </c>
       <c r="I5" t="n">
-        <v>25.93111111111111</v>
+        <v>25.64769921436588</v>
       </c>
       <c r="J5" t="n">
-        <v>181.8622222222222</v>
+        <v>182.0516273849607</v>
       </c>
       <c r="K5" t="n">
-        <v>1.38</v>
+        <v>1.375645342312009</v>
       </c>
       <c r="L5" t="n">
-        <v>75.38</v>
+        <v>75.46588103254768</v>
       </c>
       <c r="M5" t="n">
-        <v>8726222.222222222</v>
+        <v>9438698.092031427</v>
       </c>
       <c r="N5" t="n">
-        <v>79.88444444444445</v>
+        <v>80.13187429854096</v>
       </c>
       <c r="O5" t="n">
-        <v>24.63790951163074</v>
+        <v>25.25395343644704</v>
       </c>
       <c r="P5" t="n">
-        <v>186.731731823164</v>
+        <v>186.0413820890675</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.361362805991962</v>
+        <v>1.391129277798076</v>
       </c>
       <c r="R5" t="n">
-        <v>72.57060041407867</v>
+        <v>73.15978778467908</v>
       </c>
       <c r="S5" t="n">
-        <v>7044595.207648277</v>
+        <v>7081649.636666261</v>
       </c>
       <c r="T5" t="n">
-        <v>77.17188527584948</v>
+        <v>77.1639765761377</v>
       </c>
       <c r="U5" t="n">
-        <v>23.06374269005848</v>
+        <v>23.40342418546366</v>
       </c>
       <c r="V5" t="n">
-        <v>177.9514619883041</v>
+        <v>177.98210839599</v>
       </c>
       <c r="W5" t="n">
-        <v>1.354093567251462</v>
+        <v>1.39187343358396</v>
       </c>
       <c r="X5" t="n">
-        <v>72.96871345029238</v>
+        <v>73.16341791979949</v>
       </c>
       <c r="Y5" t="n">
-        <v>7907032.16374269</v>
+        <v>8325323.621553885</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.36725146198832</v>
+        <v>80.35131892230577</v>
       </c>
     </row>
     <row r="6">
@@ -893,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.1</v>
+        <v>26.33828282828283</v>
       </c>
       <c r="D6" t="n">
-        <v>184.9742424242424</v>
+        <v>185.2557575757576</v>
       </c>
       <c r="E6" t="n">
-        <v>1.506060606060606</v>
+        <v>1.529393939393939</v>
       </c>
       <c r="F6" t="n">
-        <v>77.72575757575758</v>
+        <v>77.87020202020202</v>
       </c>
       <c r="G6" t="n">
-        <v>19252575.75757575</v>
+        <v>19181949.4949495</v>
       </c>
       <c r="H6" t="n">
-        <v>80.90454545454544</v>
+        <v>80.78959595959596</v>
       </c>
       <c r="I6" t="n">
-        <v>25.62727272727273</v>
+        <v>25.4010878010878</v>
       </c>
       <c r="J6" t="n">
-        <v>179.974025974026</v>
+        <v>179.6252525252525</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>72.75844155844155</v>
+        <v>72.87241647241646</v>
       </c>
       <c r="M6" t="n">
-        <v>4395454.545454546</v>
+        <v>4502587.412587413</v>
       </c>
       <c r="N6" t="n">
-        <v>76.02987012987013</v>
+        <v>76.17327117327117</v>
       </c>
       <c r="O6" t="n">
-        <v>26.55337301587302</v>
+        <v>26.10724025974026</v>
       </c>
       <c r="P6" t="n">
-        <v>181.5990079365079</v>
+        <v>181.6400541125541</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>1.388290043290043</v>
       </c>
       <c r="R6" t="n">
-        <v>75.42678571428571</v>
+        <v>73.43741341991341</v>
       </c>
       <c r="S6" t="n">
-        <v>15324102.18253968</v>
+        <v>11666848.75541126</v>
       </c>
       <c r="T6" t="n">
-        <v>79.26924603174604</v>
+        <v>78.04791125541126</v>
       </c>
       <c r="U6" t="n">
-        <v>24.93857543017207</v>
+        <v>24.91974415184134</v>
       </c>
       <c r="V6" t="n">
-        <v>178.8070158498182</v>
+        <v>179.0702772078731</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>70.99022565547958</v>
+        <v>71.12043365841319</v>
       </c>
       <c r="Y6" t="n">
-        <v>3143829.836282339</v>
+        <v>3210330.255848159</v>
       </c>
       <c r="Z6" t="n">
-        <v>75.32631313394923</v>
+        <v>75.60448554003541</v>
       </c>
     </row>
     <row r="7">
@@ -975,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.6</v>
+        <v>25.08888888888889</v>
       </c>
       <c r="D7" t="n">
-        <v>184.86</v>
+        <v>185.0444444444444</v>
       </c>
       <c r="E7" t="n">
-        <v>1.28</v>
+        <v>1.288888888888889</v>
       </c>
       <c r="F7" t="n">
-        <v>75.25999999999999</v>
+        <v>74.94444444444444</v>
       </c>
       <c r="G7" t="n">
-        <v>8900000</v>
+        <v>8736666.666666666</v>
       </c>
       <c r="H7" t="n">
-        <v>78.67999999999999</v>
+        <v>78.77777777777777</v>
       </c>
       <c r="I7" t="n">
-        <v>24.06666666666667</v>
+        <v>24.26</v>
       </c>
       <c r="J7" t="n">
-        <v>181.4166666666667</v>
+        <v>181.46</v>
       </c>
       <c r="K7" t="n">
-        <v>1.166666666666667</v>
+        <v>1.17</v>
       </c>
       <c r="L7" t="n">
-        <v>74.89999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="M7" t="n">
-        <v>8710000</v>
+        <v>8717000</v>
       </c>
       <c r="N7" t="n">
-        <v>79.01666666666667</v>
+        <v>79.02000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>24.78453416149068</v>
+        <v>24.68995385593851</v>
       </c>
       <c r="P7" t="n">
-        <v>185.8153830227743</v>
+        <v>185.1294381520724</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.430248447204969</v>
+        <v>1.438134480845478</v>
       </c>
       <c r="R7" t="n">
-        <v>75.23780538302279</v>
+        <v>75.3371331141152</v>
       </c>
       <c r="S7" t="n">
-        <v>10522339.54451346</v>
+        <v>10891687.7765599</v>
       </c>
       <c r="T7" t="n">
-        <v>79.59751552795031</v>
+        <v>79.49908456136079</v>
       </c>
       <c r="U7" t="n">
-        <v>23.88922305764411</v>
+        <v>23.7525555737169</v>
       </c>
       <c r="V7" t="n">
-        <v>183.0538935723146</v>
+        <v>183.0730426651279</v>
       </c>
       <c r="W7" t="n">
-        <v>1.315946431735905</v>
+        <v>1.307502641650239</v>
       </c>
       <c r="X7" t="n">
-        <v>74.04833675096833</v>
+        <v>74.62954552884187</v>
       </c>
       <c r="Y7" t="n">
-        <v>10653744.2722969</v>
+        <v>11426105.25903032</v>
       </c>
       <c r="Z7" t="n">
-        <v>78.96976405660617</v>
+        <v>79.50609756439849</v>
       </c>
     </row>
     <row r="8">
@@ -1057,76 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>28.05454545454545</v>
+        <v>27.83838383838384</v>
       </c>
       <c r="D8" t="n">
-        <v>183.3272727272727</v>
+        <v>182.9545454545454</v>
       </c>
       <c r="E8" t="n">
-        <v>2.145454545454546</v>
+        <v>2.132323232323232</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>79.04848484848486</v>
       </c>
       <c r="G8" t="n">
-        <v>18487272.72727273</v>
+        <v>18862020.20202021</v>
       </c>
       <c r="H8" t="n">
-        <v>80.32727272727273</v>
+        <v>80.5010101010101</v>
       </c>
       <c r="I8" t="n">
-        <v>26.36363636363636</v>
+        <v>26.11818181818182</v>
       </c>
       <c r="J8" t="n">
-        <v>182.0181818181819</v>
+        <v>182.4777777777778</v>
       </c>
       <c r="K8" t="n">
-        <v>2.163636363636364</v>
+        <v>2.134343434343434</v>
       </c>
       <c r="L8" t="n">
-        <v>79.96363636363637</v>
+        <v>79.73535353535354</v>
       </c>
       <c r="M8" t="n">
-        <v>26307272.72727273</v>
+        <v>26002121.21212121</v>
       </c>
       <c r="N8" t="n">
-        <v>81.67272727272727</v>
+        <v>81.74747474747475</v>
       </c>
       <c r="O8" t="n">
-        <v>26.87345811051694</v>
+        <v>27.38516632242123</v>
       </c>
       <c r="P8" t="n">
-        <v>180.5931066972244</v>
+        <v>181.0887629799394</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.699712248535778</v>
+        <v>1.699134670703298</v>
       </c>
       <c r="R8" t="n">
-        <v>73.25849503437739</v>
+        <v>73.47870535419555</v>
       </c>
       <c r="S8" t="n">
-        <v>9518856.760886172</v>
+        <v>8522039.029416479</v>
       </c>
       <c r="T8" t="n">
-        <v>77.69413547237077</v>
+        <v>77.29899060634355</v>
       </c>
       <c r="U8" t="n">
-        <v>23.42254901960784</v>
+        <v>23.4527312052035</v>
       </c>
       <c r="V8" t="n">
-        <v>183.7293300653595</v>
+        <v>183.2998156831171</v>
       </c>
       <c r="W8" t="n">
-        <v>1.603349673202614</v>
+        <v>1.695527059455022</v>
       </c>
       <c r="X8" t="n">
-        <v>72.96756535947713</v>
+        <v>73.71416003599506</v>
       </c>
       <c r="Y8" t="n">
-        <v>12256787.17320262</v>
+        <v>14119290.64641154</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.08905228758169</v>
+        <v>79.37776120109879</v>
       </c>
     </row>
     <row r="9">
@@ -1139,254 +1139,328 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>25.97171717171717</v>
       </c>
       <c r="D9" t="n">
-        <v>184.6363636363637</v>
+        <v>184.5575757575758</v>
       </c>
       <c r="E9" t="n">
-        <v>1.054545454545454</v>
+        <v>1.05050505050505</v>
       </c>
       <c r="F9" t="n">
-        <v>76.92727272727272</v>
+        <v>76.47070707070708</v>
       </c>
       <c r="G9" t="n">
-        <v>12556363.63636364</v>
+        <v>11524444.44444444</v>
       </c>
       <c r="H9" t="n">
-        <v>79.41818181818181</v>
+        <v>79.06262626262627</v>
       </c>
       <c r="I9" t="n">
-        <v>25.33333333333333</v>
+        <v>25.70909090909091</v>
       </c>
       <c r="J9" t="n">
-        <v>183.6212121212121</v>
+        <v>183.6272727272728</v>
       </c>
       <c r="K9" t="n">
-        <v>1.318181818181818</v>
+        <v>1.3</v>
       </c>
       <c r="L9" t="n">
-        <v>76.54545454545455</v>
+        <v>76.56363636363636</v>
       </c>
       <c r="M9" t="n">
-        <v>14727272.72727273</v>
+        <v>14091818.18181818</v>
       </c>
       <c r="N9" t="n">
-        <v>80.25757575757575</v>
+        <v>79.99090909090908</v>
       </c>
       <c r="O9" t="n">
-        <v>24.90455108359133</v>
+        <v>24.81107480029048</v>
       </c>
       <c r="P9" t="n">
-        <v>181.333653250774</v>
+        <v>180.1133719374689</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.094922600619195</v>
+        <v>1.102232159920498</v>
       </c>
       <c r="R9" t="n">
-        <v>73.53170278637772</v>
+        <v>73.72198524634025</v>
       </c>
       <c r="S9" t="n">
-        <v>6528724.458204335</v>
+        <v>7842882.983602799</v>
       </c>
       <c r="T9" t="n">
-        <v>77.56572755417957</v>
+        <v>77.57716431601881</v>
       </c>
       <c r="U9" t="n">
-        <v>26.49900793650794</v>
+        <v>26.66244824016563</v>
       </c>
       <c r="V9" t="n">
-        <v>183.9642857142857</v>
+        <v>183.7573757763975</v>
       </c>
       <c r="W9" t="n">
-        <v>1.149140211640212</v>
+        <v>1.16104209799862</v>
       </c>
       <c r="X9" t="n">
-        <v>73.3558201058201</v>
+        <v>72.87970583160799</v>
       </c>
       <c r="Y9" t="n">
-        <v>8025330.687830688</v>
+        <v>7252254.572118702</v>
       </c>
       <c r="Z9" t="n">
-        <v>76.56316137566138</v>
+        <v>76.25773378191857</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.99671717171717</v>
+        <v>23.25555555555556</v>
       </c>
       <c r="D10" t="n">
-        <v>184.6834595959596</v>
+        <v>182.8925925925926</v>
       </c>
       <c r="E10" t="n">
-        <v>2.206060606060606</v>
+        <v>1.755555555555555</v>
       </c>
       <c r="F10" t="n">
-        <v>79.97651515151514</v>
+        <v>78.10555555555555</v>
       </c>
       <c r="G10" t="n">
-        <v>29083459.5959596</v>
+        <v>21198148.14814815</v>
       </c>
       <c r="H10" t="n">
-        <v>84.28800505050505</v>
+        <v>83.3962962962963</v>
       </c>
       <c r="I10" t="n">
-        <v>27.02045454545454</v>
+        <v>26.41136363636364</v>
       </c>
       <c r="J10" t="n">
-        <v>182.2965909090909</v>
+        <v>182.0325757575758</v>
       </c>
       <c r="K10" t="n">
-        <v>3.228409090909091</v>
+        <v>3.124242424242424</v>
       </c>
       <c r="L10" t="n">
-        <v>85.92272727272729</v>
+        <v>85.33484848484848</v>
       </c>
       <c r="M10" t="n">
-        <v>75244318.18181819</v>
+        <v>73172727.27272727</v>
       </c>
       <c r="N10" t="n">
-        <v>87.69886363636363</v>
+        <v>87.56212121212121</v>
       </c>
       <c r="O10" t="n">
-        <v>24.25017586580087</v>
+        <v>23.17500464231182</v>
       </c>
       <c r="P10" t="n">
-        <v>184.4930194805195</v>
+        <v>183.0586274168267</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.762959956709957</v>
+        <v>1.671707475954346</v>
       </c>
       <c r="R10" t="n">
-        <v>74.79669462481962</v>
+        <v>73.43256778244664</v>
       </c>
       <c r="S10" t="n">
-        <v>18135945.27867965</v>
+        <v>14940812.9466566</v>
       </c>
       <c r="T10" t="n">
-        <v>81.31994047619048</v>
+        <v>81.24884904092232</v>
       </c>
       <c r="U10" t="n">
-        <v>24.74854806052856</v>
+        <v>24.7353765781675</v>
       </c>
       <c r="V10" t="n">
-        <v>178.5162910272805</v>
+        <v>178.3245861750497</v>
       </c>
       <c r="W10" t="n">
-        <v>2.278723536516056</v>
+        <v>2.272066858144224</v>
       </c>
       <c r="X10" t="n">
-        <v>80.59222257743677</v>
+        <v>80.33949292277298</v>
       </c>
       <c r="Y10" t="n">
-        <v>44444087.45382211</v>
+        <v>44759092.84970027</v>
       </c>
       <c r="Z10" t="n">
-        <v>85.10128498863313</v>
+        <v>85.03250932015318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>26.37407407407407</v>
+      </c>
+      <c r="D11" t="n">
+        <v>182.9382716049383</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.406172839506173</v>
+      </c>
+      <c r="F11" t="n">
+        <v>75.98641975308641</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9790864.197530866</v>
+      </c>
+      <c r="H11" t="n">
+        <v>78.21728395061729</v>
+      </c>
       <c r="I11" t="n">
-        <v>24.44444444444444</v>
+        <v>24.9575</v>
       </c>
       <c r="J11" t="n">
-        <v>183.4444444444445</v>
+        <v>184.6891666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2.1275</v>
       </c>
       <c r="L11" t="n">
-        <v>69.66666666666667</v>
+        <v>81.80055555555556</v>
       </c>
       <c r="M11" t="n">
-        <v>2586111.111111111</v>
+        <v>39865000</v>
       </c>
       <c r="N11" t="n">
-        <v>74.55555555555556</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+        <v>85.05416666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>26.14814591439978</v>
+      </c>
+      <c r="P11" t="n">
+        <v>180.685791647866</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.479803936460283</v>
+      </c>
+      <c r="R11" t="n">
+        <v>73.61547176020859</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6016337.951980367</v>
+      </c>
+      <c r="T11" t="n">
+        <v>76.26133068857527</v>
+      </c>
       <c r="U11" t="n">
-        <v>23.43472222222222</v>
+        <v>24.43801426471705</v>
       </c>
       <c r="V11" t="n">
-        <v>182.5714285714286</v>
+        <v>181.8104673169108</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.75239745419699</v>
       </c>
       <c r="X11" t="n">
-        <v>68.16527777777777</v>
+        <v>78.51739375175907</v>
       </c>
       <c r="Y11" t="n">
-        <v>2176979.166666667</v>
+        <v>27403190.79854829</v>
       </c>
       <c r="Z11" t="n">
-        <v>74.02242063492064</v>
+        <v>82.04798320444606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.68215488215488</v>
+      </c>
+      <c r="D12" t="n">
+        <v>184.9391414141414</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.213636363636363</v>
+      </c>
+      <c r="F12" t="n">
+        <v>79.82323232323232</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29785223.06397307</v>
+      </c>
+      <c r="H12" t="n">
+        <v>84.46085858585859</v>
+      </c>
+      <c r="I12" t="n">
+        <v>26.41136363636364</v>
+      </c>
+      <c r="J12" t="n">
+        <v>182.0325757575758</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.124242424242424</v>
+      </c>
+      <c r="L12" t="n">
+        <v>85.33484848484848</v>
+      </c>
+      <c r="M12" t="n">
+        <v>73172727.27272727</v>
+      </c>
+      <c r="N12" t="n">
+        <v>87.56212121212121</v>
+      </c>
+      <c r="O12" t="n">
+        <v>24.36465025513938</v>
+      </c>
+      <c r="P12" t="n">
+        <v>184.0855234540017</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.862102128949955</v>
+      </c>
+      <c r="R12" t="n">
+        <v>75.34181815567685</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19042710.4997961</v>
+      </c>
+      <c r="T12" t="n">
+        <v>81.57359960892569</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.7353765781675</v>
+      </c>
+      <c r="V12" t="n">
+        <v>178.3245861750497</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.272066858144224</v>
+      </c>
+      <c r="X12" t="n">
+        <v>80.33949292277298</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>44759092.84970027</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>85.03250932015318</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1399,22 +1473,22 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>25.53939393939394</v>
+        <v>24.82575757575757</v>
       </c>
       <c r="J13" t="n">
-        <v>180.6757575757576</v>
+        <v>184.276893939394</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>70.12121212121212</v>
+        <v>69.90568181818182</v>
       </c>
       <c r="M13" t="n">
-        <v>2251969.696969697</v>
+        <v>2496268.939393939</v>
       </c>
       <c r="N13" t="n">
-        <v>73</v>
+        <v>73.95719696969697</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1423,28 +1497,28 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>21.44033613445378</v>
+        <v>24.32956495098039</v>
       </c>
       <c r="V13" t="n">
-        <v>177.9665732959851</v>
+        <v>181.4938608776844</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>65.98991596638655</v>
+        <v>69.14041053921568</v>
       </c>
       <c r="Y13" t="n">
-        <v>1754393.090569561</v>
+        <v>2337370.046977124</v>
       </c>
       <c r="Z13" t="n">
-        <v>75.46479925303454</v>
+        <v>73.8545678688142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1476,121 +1550,97 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>25.2375</v>
+      </c>
+      <c r="J15" t="n">
+        <v>180.3011363636364</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>70.11704545454546</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2284943.181818182</v>
+      </c>
+      <c r="N15" t="n">
+        <v>72.90909090909091</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>22.64599726254138</v>
+      </c>
+      <c r="V15" t="n">
+        <v>179.6302048849843</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>66.54179929547577</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1682504.416539343</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>74.4822542653425</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>23.15277777777778</v>
-      </c>
-      <c r="D16" t="n">
-        <v>181.2777777777778</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>68.45833333333333</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2093981.481481481</v>
-      </c>
-      <c r="H16" t="n">
-        <v>74.58333333333333</v>
-      </c>
-      <c r="I16" t="n">
-        <v>23.91944444444444</v>
-      </c>
-      <c r="J16" t="n">
-        <v>182.2533333333333</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>71.35111111111111</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4265277.777777778</v>
-      </c>
-      <c r="N16" t="n">
-        <v>77.18944444444443</v>
-      </c>
-      <c r="O16" t="n">
-        <v>25.8292663476874</v>
-      </c>
-      <c r="P16" t="n">
-        <v>180.2996810207337</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>67.52958532695375</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1649124.800637959</v>
-      </c>
-      <c r="T16" t="n">
-        <v>72.44808612440193</v>
-      </c>
-      <c r="U16" t="n">
-        <v>24.21920483025746</v>
-      </c>
-      <c r="V16" t="n">
-        <v>181.9104591023012</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>68.69405559352928</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2797111.187058555</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>74.53902654363181</v>
-      </c>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1622,144 +1672,142 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>23.40173611111111</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.2527777777778</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>68.55381944444446</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2099687.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>74.46041666666666</v>
+      </c>
+      <c r="I18" t="n">
+        <v>24.01972222222222</v>
+      </c>
+      <c r="J18" t="n">
+        <v>182.9066666666667</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>71.38555555555556</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4284638.888888889</v>
+      </c>
+      <c r="N18" t="n">
+        <v>77.04472222222222</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25.50162030521938</v>
+      </c>
+      <c r="P18" t="n">
+        <v>180.8198792156416</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>66.65396914746759</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1495564.161350346</v>
+      </c>
+      <c r="T18" t="n">
+        <v>72.0411998970242</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24.0197809865573</v>
+      </c>
+      <c r="V18" t="n">
+        <v>180.5749984587136</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>68.87206981357136</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2870247.557814992</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>74.91416663316045</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>182.4666666666667</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="L19" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1895833.333333333</v>
-      </c>
-      <c r="N19" t="n">
-        <v>71.89999999999999</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
-        <v>26.1699604743083</v>
-      </c>
-      <c r="V19" t="n">
-        <v>180.9741106719368</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>67.64532279314888</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1443914.690382082</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>71.43814229249011</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>26</v>
-      </c>
-      <c r="D20" t="n">
-        <v>183.2333333333333</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>68.89999999999999</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1880000</v>
-      </c>
-      <c r="H20" t="n">
-        <v>71.83333333333333</v>
-      </c>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>24.04629629629629</v>
-      </c>
-      <c r="P20" t="n">
-        <v>182.5436507936508</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>63.12169312169313</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1106871.693121693</v>
-      </c>
-      <c r="T20" t="n">
-        <v>68.84656084656085</v>
-      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
@@ -1770,7 +1818,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1783,22 +1831,22 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>25.03030303030303</v>
+        <v>27.81944444444445</v>
       </c>
       <c r="J21" t="n">
-        <v>182.2424242424242</v>
+        <v>183.2555555555556</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>1.177777777777778</v>
       </c>
       <c r="L21" t="n">
-        <v>69.3030303030303</v>
+        <v>70.75416666666666</v>
       </c>
       <c r="M21" t="n">
-        <v>2061818.181818182</v>
+        <v>1853020.833333333</v>
       </c>
       <c r="N21" t="n">
-        <v>73.51515151515152</v>
+        <v>72.01666666666668</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -1807,49 +1855,75 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>26.69074074074074</v>
+        <v>25.89903721135844</v>
       </c>
       <c r="V21" t="n">
-        <v>178.3407407407407</v>
+        <v>180.8181548392969</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>68.0351851851852</v>
+        <v>67.70345687278969</v>
       </c>
       <c r="Y21" t="n">
-        <v>1474120.37037037</v>
+        <v>1508394.780723424</v>
       </c>
       <c r="Z21" t="n">
-        <v>71.08333333333333</v>
+        <v>71.64228631422924</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.31818181818182</v>
+      </c>
+      <c r="D22" t="n">
+        <v>183.0761363636364</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>70.01931818181818</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2062954.545454546</v>
+      </c>
+      <c r="H22" t="n">
+        <v>72.26704545454545</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>24.16959586466165</v>
+      </c>
+      <c r="P22" t="n">
+        <v>182.5104845446951</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>65.26865601503761</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1512135.442773601</v>
+      </c>
+      <c r="T22" t="n">
+        <v>70.8046888053467</v>
+      </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
@@ -1860,39 +1934,65 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="J23" t="n">
+        <v>182.0454545454545</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>69.15909090909091</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2135681.818181818</v>
+      </c>
+      <c r="N23" t="n">
+        <v>74.13636363636365</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>26.41304563492064</v>
+      </c>
+      <c r="V23" t="n">
+        <v>179.4187003968254</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>67.79518849206349</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1484603.174603174</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>70.92261904761905</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1924,65 +2024,39 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>185.34</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L25" t="n">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2426000</v>
-      </c>
-      <c r="N25" t="n">
-        <v>72.86000000000001</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="n">
-        <v>27.8981884057971</v>
-      </c>
-      <c r="V25" t="n">
-        <v>183.9869565217391</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.094565217391304</v>
-      </c>
-      <c r="X25" t="n">
-        <v>70.8876811594203</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2380326.086956522</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>72.71231884057971</v>
-      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2014,65 +2088,65 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>182.65</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1638750</v>
-      </c>
-      <c r="H27" t="n">
-        <v>73.34999999999999</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>23.27250712250712</v>
-      </c>
-      <c r="P27" t="n">
-        <v>183.2507122507123</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>65.71353276353275</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1436460.113960114</v>
-      </c>
-      <c r="T27" t="n">
-        <v>73.40313390313391</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="J27" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L27" t="n">
+        <v>71.30999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2357000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>72.74000000000001</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>28.01865942028985</v>
+      </c>
+      <c r="V27" t="n">
+        <v>184.3760869565217</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.082065217391304</v>
+      </c>
+      <c r="X27" t="n">
+        <v>70.66557971014493</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2244945.652173913</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>72.43007246376813</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2104,28 +2178,54 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>24.03492063492064</v>
+      </c>
+      <c r="D29" t="n">
+        <v>182.6269841269841</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>67.4063492063492</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1687261.904761905</v>
+      </c>
+      <c r="H29" t="n">
+        <v>73.78412698412697</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>23.9511485042735</v>
+      </c>
+      <c r="P29" t="n">
+        <v>182.9341212606838</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>66.13111645299145</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1412748.063568376</v>
+      </c>
+      <c r="T29" t="n">
+        <v>72.81940438034188</v>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
@@ -2136,54 +2236,28 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>26.22888888888889</v>
-      </c>
-      <c r="D30" t="n">
-        <v>182.6111111111111</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>72.32444444444445</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3313777.777777778</v>
-      </c>
-      <c r="H30" t="n">
-        <v>74.8111111111111</v>
-      </c>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>25.76604776297871</v>
-      </c>
-      <c r="P30" t="n">
-        <v>183.9617530806789</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>69.36187597568671</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2407644.63413824</v>
-      </c>
-      <c r="T30" t="n">
-        <v>73.22434649749228</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
@@ -2194,7 +2268,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2226,258 +2300,284 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>25.56666666666667</v>
-      </c>
-      <c r="J32" t="n">
-        <v>180.3333333333333</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>69.86666666666666</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2524166.666666667</v>
-      </c>
-      <c r="N32" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="n">
-        <v>25.99801587301587</v>
-      </c>
-      <c r="V32" t="n">
-        <v>179.5912698412699</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>68.37103174603175</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1671577.380952381</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>72.96428571428572</v>
-      </c>
+      <c r="C32" t="n">
+        <v>26.15444444444444</v>
+      </c>
+      <c r="D32" t="n">
+        <v>182.4055555555555</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>72.10222222222221</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3227888.888888889</v>
+      </c>
+      <c r="H32" t="n">
+        <v>74.70555555555555</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>25.41227404309246</v>
+      </c>
+      <c r="P32" t="n">
+        <v>183.9471014918585</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>68.78982615849624</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2329014.947967634</v>
+      </c>
+      <c r="T32" t="n">
+        <v>73.52862444460911</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>26.47685185185185</v>
-      </c>
-      <c r="D33" t="n">
-        <v>184.3425925925926</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>70.14814814814814</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2017013.888888889</v>
-      </c>
-      <c r="H33" t="n">
-        <v>72.02314814814814</v>
-      </c>
-      <c r="I33" t="n">
-        <v>22.42962962962963</v>
-      </c>
-      <c r="J33" t="n">
-        <v>182.2111111111111</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>69.18888888888888</v>
-      </c>
-      <c r="M33" t="n">
-        <v>2930185.185185185</v>
-      </c>
-      <c r="N33" t="n">
-        <v>76.78148148148148</v>
-      </c>
-      <c r="O33" t="n">
-        <v>23.61013645224171</v>
-      </c>
-      <c r="P33" t="n">
-        <v>181.3713450292398</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>66.93567251461988</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1723440.545808967</v>
-      </c>
-      <c r="T33" t="n">
-        <v>73.50974658869397</v>
-      </c>
-      <c r="U33" t="n">
-        <v>22.7132857719747</v>
-      </c>
-      <c r="V33" t="n">
-        <v>181.6893256158299</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>66.28680396643783</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1836649.167676224</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>73.81612599273119</v>
-      </c>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D34" t="n">
-        <v>181.4333333333333</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1041666.666666667</v>
-      </c>
-      <c r="H34" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>26.44412393162393</v>
-      </c>
-      <c r="P34" t="n">
-        <v>183.0144230769231</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>65.60854700854701</v>
-      </c>
-      <c r="S34" t="n">
-        <v>958325.3205128206</v>
-      </c>
-      <c r="T34" t="n">
-        <v>69.13215811965811</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>25.575</v>
+      </c>
+      <c r="J34" t="n">
+        <v>180.2625</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>69.9375</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2551875</v>
+      </c>
+      <c r="N34" t="n">
+        <v>73.47499999999999</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>24.87872023809524</v>
+      </c>
+      <c r="V34" t="n">
+        <v>178.8340773809524</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>67.6547619047619</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1660279.017857143</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>73.7202380952381</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>26.73827160493827</v>
+      </c>
+      <c r="D35" t="n">
+        <v>184.3731481481481</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>69.69259259259259</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1850740.740740741</v>
+      </c>
+      <c r="H35" t="n">
+        <v>71.66697530864197</v>
+      </c>
+      <c r="I35" t="n">
+        <v>22.08194444444445</v>
+      </c>
+      <c r="J35" t="n">
+        <v>182.2559027777778</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>69.44027777777778</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3137951.388888889</v>
+      </c>
+      <c r="N35" t="n">
+        <v>77.55694444444444</v>
+      </c>
+      <c r="O35" t="n">
+        <v>23.42063563467072</v>
+      </c>
+      <c r="P35" t="n">
+        <v>181.9241344100993</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>66.54489857121436</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1645896.882519689</v>
+      </c>
+      <c r="T35" t="n">
+        <v>73.33589029553943</v>
+      </c>
+      <c r="U35" t="n">
+        <v>22.40219417429443</v>
+      </c>
+      <c r="V35" t="n">
+        <v>181.3653292137793</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>66.24453065408085</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1755605.417045251</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>73.74275067864674</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>26.7375</v>
+      </c>
+      <c r="D36" t="n">
+        <v>181.825</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>66.825</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1085937.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>69.32499999999999</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>27.49273125449112</v>
+      </c>
+      <c r="P36" t="n">
+        <v>182.0877166966805</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>65.55685345356397</v>
+      </c>
+      <c r="S36" t="n">
+        <v>871766.9741168919</v>
+      </c>
+      <c r="T36" t="n">
+        <v>68.23378406133341</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
@@ -2488,54 +2588,28 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>24.20833333333333</v>
-      </c>
-      <c r="D37" t="n">
-        <v>179.7916666666667</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>68.79166666666667</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1970833.333333333</v>
-      </c>
-      <c r="H37" t="n">
-        <v>74.5</v>
-      </c>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>24.39869281045752</v>
-      </c>
-      <c r="P37" t="n">
-        <v>180.2530204000792</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>67.35244602891662</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1574286.987522282</v>
-      </c>
-      <c r="T37" t="n">
-        <v>72.71548821548822</v>
-      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
@@ -2546,7 +2620,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2578,28 +2652,54 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>24.69642857142857</v>
+      </c>
+      <c r="D39" t="n">
+        <v>179.9642857142857</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>68.98214285714286</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1917857.142857143</v>
+      </c>
+      <c r="H39" t="n">
+        <v>73.78571428571429</v>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>24.66104906875031</v>
+      </c>
+      <c r="P39" t="n">
+        <v>179.4951541621433</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>67.50847260754381</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1584282.536778667</v>
+      </c>
+      <c r="T39" t="n">
+        <v>72.88109003569531</v>
+      </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
@@ -2610,54 +2710,28 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>24.12121212121212</v>
-      </c>
-      <c r="D40" t="n">
-        <v>183.7575757575758</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2534545.454545455</v>
-      </c>
-      <c r="H40" t="n">
-        <v>74.24242424242424</v>
-      </c>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>23.6031746031746</v>
-      </c>
-      <c r="P40" t="n">
-        <v>181.4146825396825</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>67.31547619047619</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1888819.444444445</v>
-      </c>
-      <c r="T40" t="n">
-        <v>73.60317460317459</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
@@ -2668,7 +2742,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2700,29 +2774,29 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>23.9469696969697</v>
+        <v>24.19545454545455</v>
       </c>
       <c r="D42" t="n">
-        <v>181.6301346801347</v>
+        <v>183.3590909090909</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>71.23400673400674</v>
+        <v>69.87613636363636</v>
       </c>
       <c r="G42" t="n">
-        <v>3912899.831649832</v>
+        <v>2527954.545454545</v>
       </c>
       <c r="H42" t="n">
-        <v>77.02205387205389</v>
+        <v>74.09090909090909</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -2731,22 +2805,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>23.05900300966091</v>
+        <v>24.049227915804</v>
       </c>
       <c r="P42" t="n">
-        <v>179.9004198530514</v>
+        <v>182.4102462905452</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>68.90433348328084</v>
+        <v>68.46791105935128</v>
       </c>
       <c r="S42" t="n">
-        <v>2854691.814338196</v>
+        <v>2306720.637077295</v>
       </c>
       <c r="T42" t="n">
-        <v>76.35960587901377</v>
+        <v>74.24992236024845</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -2758,111 +2832,61 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>24</v>
-      </c>
-      <c r="D43" t="n">
-        <v>179.9090909090909</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="F43" t="n">
-        <v>69.65909090909092</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3025000</v>
-      </c>
-      <c r="H43" t="n">
-        <v>75.06818181818183</v>
-      </c>
-      <c r="I43" t="n">
-        <v>27.16363636363636</v>
-      </c>
-      <c r="J43" t="n">
-        <v>182.0060606060606</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>67.67878787878789</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1262727.272727273</v>
-      </c>
-      <c r="N43" t="n">
-        <v>70.35151515151516</v>
-      </c>
-      <c r="O43" t="n">
-        <v>25.18951914098973</v>
-      </c>
-      <c r="P43" t="n">
-        <v>180.955987394958</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.0125</v>
-      </c>
-      <c r="R43" t="n">
-        <v>70.16818394024276</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2982754.726890756</v>
-      </c>
-      <c r="T43" t="n">
-        <v>74.78092903828198</v>
-      </c>
-      <c r="U43" t="n">
-        <v>25.92451690821256</v>
-      </c>
-      <c r="V43" t="n">
-        <v>185.8272946859903</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>66.48128019323671</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1146784.420289855</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>70.07910628019323</v>
-      </c>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>24.39393939393939</v>
+        <v>24.03818181818182</v>
       </c>
       <c r="D44" t="n">
-        <v>181.2424242424242</v>
+        <v>182.3655808080808</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>68.24242424242425</v>
+        <v>71.67818181818181</v>
       </c>
       <c r="G44" t="n">
-        <v>2218939.393939394</v>
+        <v>4148545.454545455</v>
       </c>
       <c r="H44" t="n">
-        <v>73.93939393939394</v>
+        <v>77.17017676767678</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -2871,22 +2895,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>24</v>
+        <v>23.23972415011889</v>
       </c>
       <c r="P44" t="n">
-        <v>181.7615942028986</v>
+        <v>180.0264973330763</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>66.23985507246377</v>
+        <v>69.24250851487693</v>
       </c>
       <c r="S44" t="n">
-        <v>1441865.942028986</v>
+        <v>2863183.678346507</v>
       </c>
       <c r="T44" t="n">
-        <v>72.92318840579711</v>
+        <v>76.43462799627272</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
@@ -2898,83 +2922,223 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>24.2050505050505</v>
+      </c>
+      <c r="D45" t="n">
+        <v>179.6383838383839</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.093939393939394</v>
+      </c>
+      <c r="F45" t="n">
+        <v>70.02121212121213</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3147020.202020202</v>
+      </c>
+      <c r="H45" t="n">
+        <v>75.11414141414143</v>
+      </c>
+      <c r="I45" t="n">
+        <v>26.69772727272727</v>
+      </c>
+      <c r="J45" t="n">
+        <v>183.0136363636364</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>67.42500000000001</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1249943.181818182</v>
+      </c>
+      <c r="N45" t="n">
+        <v>70.65454545454546</v>
+      </c>
+      <c r="O45" t="n">
+        <v>25.63840771413235</v>
+      </c>
+      <c r="P45" t="n">
+        <v>180.4452573783137</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.021552050772</v>
+      </c>
+      <c r="R45" t="n">
+        <v>70.2869620472988</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3089030.458801878</v>
+      </c>
+      <c r="T45" t="n">
+        <v>74.53751178410172</v>
+      </c>
+      <c r="U45" t="n">
+        <v>25.72169384057971</v>
+      </c>
+      <c r="V45" t="n">
+        <v>184.5289855072464</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.015625</v>
+      </c>
+      <c r="X45" t="n">
+        <v>66.62839673913044</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1802179.574275362</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>70.3629981884058</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>24.02272727272727</v>
+      </c>
+      <c r="D46" t="n">
+        <v>181.2386363636364</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>67.97727272727272</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2198011.363636364</v>
+      </c>
+      <c r="H46" t="n">
+        <v>74.15909090909091</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>24.72708333333333</v>
+      </c>
+      <c r="P46" t="n">
+        <v>180.9827704451346</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>66.45497541407867</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1385517.436594203</v>
+      </c>
+      <c r="T46" t="n">
+        <v>72.04039208074533</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>22.85925925925926</v>
-      </c>
-      <c r="D45" t="n">
-        <v>184.7222222222223</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1.233333333333333</v>
-      </c>
-      <c r="F45" t="n">
-        <v>74.34074074074074</v>
-      </c>
-      <c r="G45" t="n">
-        <v>8813703.703703703</v>
-      </c>
-      <c r="H45" t="n">
-        <v>80.6962962962963</v>
-      </c>
-      <c r="I45" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J45" t="n">
-        <v>182.2666666666667</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1.066666666666667</v>
-      </c>
-      <c r="L45" t="n">
-        <v>69.13333333333334</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2423333.333333333</v>
-      </c>
-      <c r="N45" t="n">
-        <v>75.60000000000001</v>
-      </c>
-      <c r="O45" t="n">
-        <v>24.44442007797271</v>
-      </c>
-      <c r="P45" t="n">
-        <v>179.8515229044834</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.019188596491228</v>
-      </c>
-      <c r="R45" t="n">
-        <v>73.15342348927875</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5622342.83625731</v>
-      </c>
-      <c r="T45" t="n">
-        <v>77.49465155945418</v>
-      </c>
-      <c r="U45" t="n">
-        <v>22.65073099415205</v>
-      </c>
-      <c r="V45" t="n">
-        <v>179.8783625730995</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.017543859649123</v>
-      </c>
-      <c r="X45" t="n">
-        <v>66.61827485380117</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1908505.116959064</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>74.17690058479532</v>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>23.15876951331497</v>
+      </c>
+      <c r="D47" t="n">
+        <v>184.1435261707989</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.240495867768595</v>
+      </c>
+      <c r="F47" t="n">
+        <v>74.33544536271808</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8546896.235078054</v>
+      </c>
+      <c r="H47" t="n">
+        <v>80.26988062442609</v>
+      </c>
+      <c r="I47" t="n">
+        <v>24.275</v>
+      </c>
+      <c r="J47" t="n">
+        <v>181.825</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="L47" t="n">
+        <v>69.92500000000001</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2531250</v>
+      </c>
+      <c r="N47" t="n">
+        <v>75.6375</v>
+      </c>
+      <c r="O47" t="n">
+        <v>24.74341362541827</v>
+      </c>
+      <c r="P47" t="n">
+        <v>180.7574865193286</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.06757116722287</v>
+      </c>
+      <c r="R47" t="n">
+        <v>73.15568706749046</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5394640.210151047</v>
+      </c>
+      <c r="T47" t="n">
+        <v>77.28504103395744</v>
+      </c>
+      <c r="U47" t="n">
+        <v>22.20630281633571</v>
+      </c>
+      <c r="V47" t="n">
+        <v>179.3947324240087</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.006578947368421</v>
+      </c>
+      <c r="X47" t="n">
+        <v>65.82074195906434</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1884488.945721676</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>74.07281665702718</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.68215488215488</v>
+        <v>24.69458218549128</v>
       </c>
       <c r="D2" t="n">
-        <v>184.9391414141414</v>
+        <v>184.834435261708</v>
       </c>
       <c r="E2" t="n">
-        <v>2.213636363636363</v>
+        <v>2.216528925619834</v>
       </c>
       <c r="F2" t="n">
-        <v>79.82323232323232</v>
+        <v>79.80716253443525</v>
       </c>
       <c r="G2" t="n">
-        <v>29785223.06397307</v>
+        <v>29811152.43342516</v>
       </c>
       <c r="H2" t="n">
-        <v>84.46085858585859</v>
+        <v>84.48622589531681</v>
       </c>
       <c r="I2" t="n">
-        <v>26.86969696969697</v>
+        <v>27.02857142857143</v>
       </c>
       <c r="J2" t="n">
-        <v>184.1666666666667</v>
+        <v>184.0389610389611</v>
       </c>
       <c r="K2" t="n">
-        <v>1.525252525252525</v>
+        <v>1.54025974025974</v>
       </c>
       <c r="L2" t="n">
-        <v>77.09696969696968</v>
+        <v>77.08441558441557</v>
       </c>
       <c r="M2" t="n">
-        <v>12918585.85858586</v>
+        <v>12791168.83116883</v>
       </c>
       <c r="N2" t="n">
-        <v>79.13232323232323</v>
+        <v>79.01948051948052</v>
       </c>
       <c r="O2" t="n">
-        <v>24.36465025513938</v>
+        <v>24.19578007631368</v>
       </c>
       <c r="P2" t="n">
-        <v>184.0855234540017</v>
+        <v>184.1286518488099</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.862102128949955</v>
+        <v>1.814212423500961</v>
       </c>
       <c r="R2" t="n">
-        <v>75.34181815567685</v>
+        <v>74.94865010922322</v>
       </c>
       <c r="S2" t="n">
-        <v>19042710.4997961</v>
+        <v>18114850.84826241</v>
       </c>
       <c r="T2" t="n">
-        <v>81.57359960892569</v>
+        <v>81.41362381579773</v>
       </c>
       <c r="U2" t="n">
-        <v>28.18738074940121</v>
+        <v>27.850611983924</v>
       </c>
       <c r="V2" t="n">
-        <v>181.4010849267243</v>
+        <v>181.5837078309584</v>
       </c>
       <c r="W2" t="n">
-        <v>1.306216254617789</v>
+        <v>1.286563755937158</v>
       </c>
       <c r="X2" t="n">
-        <v>74.99756728778468</v>
+        <v>74.9262939958592</v>
       </c>
       <c r="Y2" t="n">
-        <v>6996646.165712661</v>
+        <v>7130381.804895871</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.20626666125388</v>
+        <v>76.38934965290466</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.34090909090909</v>
+        <v>26.24242424242424</v>
       </c>
       <c r="D3" t="n">
-        <v>182.5681818181818</v>
+        <v>182.5909090909091</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>70.88636363636363</v>
+        <v>70.78787878787878</v>
       </c>
       <c r="G3" t="n">
-        <v>2750000</v>
+        <v>2710606.060606061</v>
       </c>
       <c r="H3" t="n">
-        <v>74.39772727272728</v>
+        <v>74.42424242424242</v>
       </c>
       <c r="I3" t="n">
-        <v>25.72272727272728</v>
+        <v>25.78282828282828</v>
       </c>
       <c r="J3" t="n">
-        <v>183.3354545454545</v>
+        <v>183.2818181818182</v>
       </c>
       <c r="K3" t="n">
-        <v>2.621818181818182</v>
+        <v>2.65050505050505</v>
       </c>
       <c r="L3" t="n">
-        <v>82.80363636363636</v>
+        <v>82.9939393939394</v>
       </c>
       <c r="M3" t="n">
-        <v>46842090.90909091</v>
+        <v>47821515.15151516</v>
       </c>
       <c r="N3" t="n">
-        <v>85.60454545454544</v>
+        <v>85.71212121212119</v>
       </c>
       <c r="O3" t="n">
-        <v>25.15104166666667</v>
+        <v>25.39583333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>183.3184523809524</v>
+        <v>183.5218253968254</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>68.9985119047619</v>
+        <v>69.22023809523809</v>
       </c>
       <c r="S3" t="n">
-        <v>2202232.142857143</v>
+        <v>2214087.301587302</v>
       </c>
       <c r="T3" t="n">
-        <v>73.44122023809524</v>
+        <v>73.36607142857143</v>
       </c>
       <c r="U3" t="n">
-        <v>23.29439745463403</v>
+        <v>23.45782723717506</v>
       </c>
       <c r="V3" t="n">
-        <v>183.5194333820485</v>
+        <v>183.5836841499885</v>
       </c>
       <c r="W3" t="n">
-        <v>1.813264827670199</v>
+        <v>1.851340004600874</v>
       </c>
       <c r="X3" t="n">
-        <v>79.55400590671051</v>
+        <v>79.82471244536461</v>
       </c>
       <c r="Y3" t="n">
-        <v>34401151.77810254</v>
+        <v>34862064.06717276</v>
       </c>
       <c r="Z3" t="n">
-        <v>84.53704938497137</v>
+        <v>84.58364964343225</v>
       </c>
     </row>
     <row r="4">
@@ -729,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>24.45416666666667</v>
+        <v>24.43055555555556</v>
       </c>
       <c r="D4" t="n">
-        <v>182.8930555555555</v>
+        <v>182.8194444444445</v>
       </c>
       <c r="E4" t="n">
-        <v>2.236111111111111</v>
+        <v>2.237654320987654</v>
       </c>
       <c r="F4" t="n">
-        <v>83.40416666666667</v>
+        <v>83.39969135802468</v>
       </c>
       <c r="G4" t="n">
-        <v>58345833.33333334</v>
+        <v>58353395.0617284</v>
       </c>
       <c r="H4" t="n">
-        <v>86.30833333333332</v>
+        <v>86.29320987654322</v>
       </c>
       <c r="I4" t="n">
-        <v>26.37962962962963</v>
+        <v>26.30208333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>182.8317901234568</v>
+        <v>182.9357638888889</v>
       </c>
       <c r="K4" t="n">
-        <v>1.447530864197531</v>
+        <v>1.440972222222222</v>
       </c>
       <c r="L4" t="n">
-        <v>76.59567901234567</v>
+        <v>76.57638888888889</v>
       </c>
       <c r="M4" t="n">
-        <v>12223804.01234568</v>
+        <v>12390842.01388889</v>
       </c>
       <c r="N4" t="n">
-        <v>79.56327160493828</v>
+        <v>79.60243055555556</v>
       </c>
       <c r="O4" t="n">
-        <v>24.63040227574283</v>
+        <v>24.62855154821099</v>
       </c>
       <c r="P4" t="n">
-        <v>179.6681381930763</v>
+        <v>179.6639443975357</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.772715612560814</v>
+        <v>1.786677478008747</v>
       </c>
       <c r="R4" t="n">
-        <v>81.20040006433194</v>
+        <v>81.20959484272177</v>
       </c>
       <c r="S4" t="n">
-        <v>37424843.79397692</v>
+        <v>37511264.34624887</v>
       </c>
       <c r="T4" t="n">
-        <v>84.53740098910377</v>
+        <v>84.5578965238408</v>
       </c>
       <c r="U4" t="n">
-        <v>23.99087871193134</v>
+        <v>24.26935235816815</v>
       </c>
       <c r="V4" t="n">
-        <v>181.2875089238247</v>
+        <v>180.845497265892</v>
       </c>
       <c r="W4" t="n">
-        <v>1.278936735778841</v>
+        <v>1.306012189564821</v>
       </c>
       <c r="X4" t="n">
-        <v>71.77806789701526</v>
+        <v>72.07079915698337</v>
       </c>
       <c r="Y4" t="n">
-        <v>8070421.128579023</v>
+        <v>8237183.156755526</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.70129186602871</v>
+        <v>78.62661483253589</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27.2</v>
+        <v>27.35227272727273</v>
       </c>
       <c r="D5" t="n">
-        <v>183.8545454545455</v>
+        <v>183.6363636363637</v>
       </c>
       <c r="E5" t="n">
-        <v>1.581818181818181</v>
+        <v>1.59090909090909</v>
       </c>
       <c r="F5" t="n">
-        <v>76.67272727272727</v>
+        <v>76.625</v>
       </c>
       <c r="G5" t="n">
-        <v>11300000</v>
+        <v>11089488.63636364</v>
       </c>
       <c r="H5" t="n">
-        <v>79.18181818181817</v>
+        <v>79.11363636363636</v>
       </c>
       <c r="I5" t="n">
-        <v>25.64769921436588</v>
+        <v>25.67184343434343</v>
       </c>
       <c r="J5" t="n">
-        <v>182.0516273849607</v>
+        <v>182.0694444444445</v>
       </c>
       <c r="K5" t="n">
-        <v>1.375645342312009</v>
+        <v>1.377146464646464</v>
       </c>
       <c r="L5" t="n">
-        <v>75.46588103254768</v>
+        <v>75.41047979797979</v>
       </c>
       <c r="M5" t="n">
-        <v>9438698.092031427</v>
+        <v>9254898.989898989</v>
       </c>
       <c r="N5" t="n">
-        <v>80.13187429854096</v>
+        <v>80.11426767676768</v>
       </c>
       <c r="O5" t="n">
-        <v>25.25395343644704</v>
+        <v>24.87299735111436</v>
       </c>
       <c r="P5" t="n">
-        <v>186.0413820890675</v>
+        <v>186.2774220557788</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.391129277798076</v>
+        <v>1.358703263914262</v>
       </c>
       <c r="R5" t="n">
-        <v>73.15978778467908</v>
+        <v>72.80910973084886</v>
       </c>
       <c r="S5" t="n">
-        <v>7081649.636666261</v>
+        <v>7070638.434721715</v>
       </c>
       <c r="T5" t="n">
-        <v>77.1639765761377</v>
+        <v>77.10427627572768</v>
       </c>
       <c r="U5" t="n">
-        <v>23.40342418546366</v>
+        <v>23.43655318852687</v>
       </c>
       <c r="V5" t="n">
-        <v>177.98210839599</v>
+        <v>177.9099450013924</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39187343358396</v>
+        <v>1.406175160122529</v>
       </c>
       <c r="X5" t="n">
-        <v>73.16341791979949</v>
+        <v>73.04707254246728</v>
       </c>
       <c r="Y5" t="n">
-        <v>8325323.621553885</v>
+        <v>8271997.006404902</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.35131892230577</v>
+        <v>80.20906780840993</v>
       </c>
     </row>
     <row r="6">
@@ -893,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.33828282828283</v>
+        <v>26.20568181818182</v>
       </c>
       <c r="D6" t="n">
-        <v>185.2557575757576</v>
+        <v>185.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.529393939393939</v>
+        <v>1.510227272727273</v>
       </c>
       <c r="F6" t="n">
-        <v>77.87020202020202</v>
+        <v>77.78977272727272</v>
       </c>
       <c r="G6" t="n">
-        <v>19181949.4949495</v>
+        <v>19209886.36363636</v>
       </c>
       <c r="H6" t="n">
-        <v>80.78959595959596</v>
+        <v>80.83295454545454</v>
       </c>
       <c r="I6" t="n">
-        <v>25.4010878010878</v>
+        <v>25.43966942148761</v>
       </c>
       <c r="J6" t="n">
-        <v>179.6252525252525</v>
+        <v>179.7247933884298</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>72.87241647241646</v>
+        <v>72.88760330578511</v>
       </c>
       <c r="M6" t="n">
-        <v>4502587.412587413</v>
+        <v>4517603.305785124</v>
       </c>
       <c r="N6" t="n">
-        <v>76.17327117327117</v>
+        <v>76.13305785123967</v>
       </c>
       <c r="O6" t="n">
-        <v>26.10724025974026</v>
+        <v>26.30639880952381</v>
       </c>
       <c r="P6" t="n">
-        <v>181.6400541125541</v>
+        <v>181.6296130952381</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.388290043290043</v>
+        <v>1.423809523809524</v>
       </c>
       <c r="R6" t="n">
-        <v>73.43741341991341</v>
+        <v>74.21532738095237</v>
       </c>
       <c r="S6" t="n">
-        <v>11666848.75541126</v>
+        <v>13207377.23214286</v>
       </c>
       <c r="T6" t="n">
-        <v>78.04791125541126</v>
+        <v>78.5248511904762</v>
       </c>
       <c r="U6" t="n">
-        <v>24.91974415184134</v>
+        <v>24.89665415573344</v>
       </c>
       <c r="V6" t="n">
-        <v>179.0702772078731</v>
+        <v>179.1119086369726</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>71.12043365841319</v>
+        <v>71.01268641844089</v>
       </c>
       <c r="Y6" t="n">
-        <v>3210330.255848159</v>
+        <v>3153749.986160472</v>
       </c>
       <c r="Z6" t="n">
-        <v>75.60448554003541</v>
+        <v>75.56261334573354</v>
       </c>
     </row>
     <row r="7">
@@ -975,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.08888888888889</v>
+        <v>25.18571428571429</v>
       </c>
       <c r="D7" t="n">
-        <v>185.0444444444444</v>
+        <v>184.9428571428571</v>
       </c>
       <c r="E7" t="n">
-        <v>1.288888888888889</v>
+        <v>1.271428571428572</v>
       </c>
       <c r="F7" t="n">
-        <v>74.94444444444444</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>8736666.666666666</v>
+        <v>8711428.571428571</v>
       </c>
       <c r="H7" t="n">
-        <v>78.77777777777777</v>
+        <v>78.77142857142857</v>
       </c>
       <c r="I7" t="n">
-        <v>24.26</v>
+        <v>24.2</v>
       </c>
       <c r="J7" t="n">
-        <v>181.46</v>
+        <v>181.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1.17</v>
+        <v>1.1625</v>
       </c>
       <c r="L7" t="n">
-        <v>75.05</v>
+        <v>75.03749999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>8717000</v>
+        <v>8823750</v>
       </c>
       <c r="N7" t="n">
-        <v>79.02000000000001</v>
+        <v>79.0625</v>
       </c>
       <c r="O7" t="n">
-        <v>24.68995385593851</v>
+        <v>24.74702750665483</v>
       </c>
       <c r="P7" t="n">
-        <v>185.1294381520724</v>
+        <v>185.5041555752736</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.438134480845478</v>
+        <v>1.438065661047027</v>
       </c>
       <c r="R7" t="n">
-        <v>75.3371331141152</v>
+        <v>75.36302868973677</v>
       </c>
       <c r="S7" t="n">
-        <v>10891687.7765599</v>
+        <v>10884310.85477669</v>
       </c>
       <c r="T7" t="n">
-        <v>79.49908456136079</v>
+        <v>79.63207630878438</v>
       </c>
       <c r="U7" t="n">
-        <v>23.7525555737169</v>
+        <v>23.84694446714613</v>
       </c>
       <c r="V7" t="n">
-        <v>183.0730426651279</v>
+        <v>183.1413033314099</v>
       </c>
       <c r="W7" t="n">
-        <v>1.307502641650239</v>
+        <v>1.321878302062799</v>
       </c>
       <c r="X7" t="n">
-        <v>74.62954552884187</v>
+        <v>74.41193191105233</v>
       </c>
       <c r="Y7" t="n">
-        <v>11426105.25903032</v>
+        <v>11123256.5737879</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.50609756439849</v>
+        <v>79.2701219554981</v>
       </c>
     </row>
     <row r="8">
@@ -1057,76 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.83838383838384</v>
+        <v>27.92207792207792</v>
       </c>
       <c r="D8" t="n">
-        <v>182.9545454545454</v>
+        <v>183.0324675324675</v>
       </c>
       <c r="E8" t="n">
-        <v>2.132323232323232</v>
+        <v>2.144155844155844</v>
       </c>
       <c r="F8" t="n">
-        <v>79.04848484848486</v>
+        <v>79.02337662337663</v>
       </c>
       <c r="G8" t="n">
-        <v>18862020.20202021</v>
+        <v>18771948.05194806</v>
       </c>
       <c r="H8" t="n">
-        <v>80.5010101010101</v>
+        <v>80.47532467532469</v>
       </c>
       <c r="I8" t="n">
-        <v>26.11818181818182</v>
+        <v>26.17045454545455</v>
       </c>
       <c r="J8" t="n">
-        <v>182.4777777777778</v>
+        <v>182.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.134343434343434</v>
+        <v>2.113636363636364</v>
       </c>
       <c r="L8" t="n">
-        <v>79.73535353535354</v>
+        <v>79.60227272727272</v>
       </c>
       <c r="M8" t="n">
-        <v>26002121.21212121</v>
+        <v>25338636.36363636</v>
       </c>
       <c r="N8" t="n">
-        <v>81.74747474747475</v>
+        <v>81.59090909090909</v>
       </c>
       <c r="O8" t="n">
-        <v>27.38516632242123</v>
+        <v>27.20553130343046</v>
       </c>
       <c r="P8" t="n">
-        <v>181.0887629799394</v>
+        <v>180.9712666884936</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.699134670703298</v>
+        <v>1.724284259158208</v>
       </c>
       <c r="R8" t="n">
-        <v>73.47870535419555</v>
+        <v>73.62341482047364</v>
       </c>
       <c r="S8" t="n">
-        <v>8522039.029416479</v>
+        <v>9321292.244170396</v>
       </c>
       <c r="T8" t="n">
-        <v>77.29899060634355</v>
+        <v>77.50941649387028</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4527312052035</v>
+        <v>23.48214869281045</v>
       </c>
       <c r="V8" t="n">
-        <v>183.2998156831171</v>
+        <v>183.3155535130719</v>
       </c>
       <c r="W8" t="n">
-        <v>1.695527059455022</v>
+        <v>1.711815767973856</v>
       </c>
       <c r="X8" t="n">
-        <v>73.71416003599506</v>
+        <v>73.77625612745098</v>
       </c>
       <c r="Y8" t="n">
-        <v>14119290.64641154</v>
+        <v>14425370.45547386</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.37776120109879</v>
+        <v>79.41954656862745</v>
       </c>
     </row>
     <row r="9">
@@ -1139,76 +1139,76 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.97171717171717</v>
+        <v>25.95568181818182</v>
       </c>
       <c r="D9" t="n">
-        <v>184.5575757575758</v>
+        <v>184.4272727272727</v>
       </c>
       <c r="E9" t="n">
-        <v>1.05050505050505</v>
+        <v>1.056818181818182</v>
       </c>
       <c r="F9" t="n">
-        <v>76.47070707070708</v>
+        <v>76.55454545454546</v>
       </c>
       <c r="G9" t="n">
-        <v>11524444.44444444</v>
+        <v>11720000</v>
       </c>
       <c r="H9" t="n">
-        <v>79.06262626262627</v>
+        <v>79.12045454545455</v>
       </c>
       <c r="I9" t="n">
-        <v>25.70909090909091</v>
+        <v>25.53409090909091</v>
       </c>
       <c r="J9" t="n">
-        <v>183.6272727272728</v>
+        <v>183.5454545454546</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3</v>
+        <v>1.306818181818182</v>
       </c>
       <c r="L9" t="n">
-        <v>76.56363636363636</v>
+        <v>76.57954545454545</v>
       </c>
       <c r="M9" t="n">
-        <v>14091818.18181818</v>
+        <v>14560227.27272728</v>
       </c>
       <c r="N9" t="n">
-        <v>79.99090909090908</v>
+        <v>80.13636363636363</v>
       </c>
       <c r="O9" t="n">
-        <v>24.81107480029048</v>
+        <v>24.86640651874785</v>
       </c>
       <c r="P9" t="n">
-        <v>180.1133719374689</v>
+        <v>180.4564907980736</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.102232159920498</v>
+        <v>1.095274337805298</v>
       </c>
       <c r="R9" t="n">
-        <v>73.72198524634025</v>
+        <v>73.88460182318542</v>
       </c>
       <c r="S9" t="n">
-        <v>7842882.983602799</v>
+        <v>7821598.619711042</v>
       </c>
       <c r="T9" t="n">
-        <v>77.57716431601881</v>
+        <v>77.71509932920537</v>
       </c>
       <c r="U9" t="n">
-        <v>26.66244824016563</v>
+        <v>26.62493530020704</v>
       </c>
       <c r="V9" t="n">
-        <v>183.7573757763975</v>
+        <v>183.8685947204969</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16104209799862</v>
+        <v>1.154427622498275</v>
       </c>
       <c r="X9" t="n">
-        <v>72.87970583160799</v>
+        <v>73.32619478951</v>
       </c>
       <c r="Y9" t="n">
-        <v>7252254.572118702</v>
+        <v>8194615.090148378</v>
       </c>
       <c r="Z9" t="n">
-        <v>76.25773378191857</v>
+        <v>76.50185472739821</v>
       </c>
     </row>
     <row r="10">
@@ -1221,76 +1221,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>23.25555555555556</v>
+        <v>23.35151515151515</v>
       </c>
       <c r="D10" t="n">
-        <v>182.8925925925926</v>
+        <v>182.9464646464646</v>
       </c>
       <c r="E10" t="n">
-        <v>1.755555555555555</v>
+        <v>1.760606060606061</v>
       </c>
       <c r="F10" t="n">
-        <v>78.10555555555555</v>
+        <v>78.08787878787879</v>
       </c>
       <c r="G10" t="n">
-        <v>21198148.14814815</v>
+        <v>20875252.52525252</v>
       </c>
       <c r="H10" t="n">
-        <v>83.3962962962963</v>
+        <v>83.33232323232323</v>
       </c>
       <c r="I10" t="n">
-        <v>26.41136363636364</v>
+        <v>26.40330578512397</v>
       </c>
       <c r="J10" t="n">
-        <v>182.0325757575758</v>
+        <v>181.9264462809917</v>
       </c>
       <c r="K10" t="n">
-        <v>3.124242424242424</v>
+        <v>3.108264462809917</v>
       </c>
       <c r="L10" t="n">
-        <v>85.33484848484848</v>
+        <v>85.27438016528926</v>
       </c>
       <c r="M10" t="n">
-        <v>73172727.27272727</v>
+        <v>72288429.75206612</v>
       </c>
       <c r="N10" t="n">
-        <v>87.56212121212121</v>
+        <v>87.5495867768595</v>
       </c>
       <c r="O10" t="n">
-        <v>23.17500464231182</v>
+        <v>23.1324725968077</v>
       </c>
       <c r="P10" t="n">
-        <v>183.0586274168267</v>
+        <v>183.2198013378369</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.671707475954346</v>
+        <v>1.641862701041105</v>
       </c>
       <c r="R10" t="n">
-        <v>73.43256778244664</v>
+        <v>73.50435965877296</v>
       </c>
       <c r="S10" t="n">
-        <v>14940812.9466566</v>
+        <v>15074880.35739161</v>
       </c>
       <c r="T10" t="n">
-        <v>81.24884904092232</v>
+        <v>81.27796518749969</v>
       </c>
       <c r="U10" t="n">
-        <v>24.7353765781675</v>
+        <v>24.8236193686961</v>
       </c>
       <c r="V10" t="n">
-        <v>178.3245861750497</v>
+        <v>178.5573025652949</v>
       </c>
       <c r="W10" t="n">
-        <v>2.272066858144224</v>
+        <v>2.29145261530172</v>
       </c>
       <c r="X10" t="n">
-        <v>80.33949292277298</v>
+        <v>80.48265538099298</v>
       </c>
       <c r="Y10" t="n">
-        <v>44759092.84970027</v>
+        <v>45657085.24780136</v>
       </c>
       <c r="Z10" t="n">
-        <v>85.03250932015318</v>
+        <v>85.09963583588903</v>
       </c>
     </row>
     <row r="11">
@@ -1303,76 +1303,76 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.37407407407407</v>
+        <v>26.44126984126984</v>
       </c>
       <c r="D11" t="n">
-        <v>182.9382716049383</v>
+        <v>182.8444444444444</v>
       </c>
       <c r="E11" t="n">
-        <v>1.406172839506173</v>
+        <v>1.431746031746032</v>
       </c>
       <c r="F11" t="n">
-        <v>75.98641975308641</v>
+        <v>75.93333333333332</v>
       </c>
       <c r="G11" t="n">
-        <v>9790864.197530866</v>
+        <v>9686507.936507937</v>
       </c>
       <c r="H11" t="n">
-        <v>78.21728395061729</v>
+        <v>78.16825396825395</v>
       </c>
       <c r="I11" t="n">
-        <v>24.9575</v>
+        <v>24.83055555555556</v>
       </c>
       <c r="J11" t="n">
-        <v>184.6891666666666</v>
+        <v>184.8805555555555</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1275</v>
+        <v>2.084722222222222</v>
       </c>
       <c r="L11" t="n">
-        <v>81.80055555555556</v>
+        <v>81.71944444444445</v>
       </c>
       <c r="M11" t="n">
-        <v>39865000</v>
+        <v>39532638.8888889</v>
       </c>
       <c r="N11" t="n">
-        <v>85.05416666666667</v>
+        <v>85.09722222222223</v>
       </c>
       <c r="O11" t="n">
-        <v>26.14814591439978</v>
+        <v>25.9965957674936</v>
       </c>
       <c r="P11" t="n">
-        <v>180.685791647866</v>
+        <v>180.8084482596867</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.479803936460283</v>
+        <v>1.436927881200327</v>
       </c>
       <c r="R11" t="n">
-        <v>73.61547176020859</v>
+        <v>73.55940988835725</v>
       </c>
       <c r="S11" t="n">
-        <v>6016337.951980367</v>
+        <v>5927105.196145444</v>
       </c>
       <c r="T11" t="n">
-        <v>76.26133068857527</v>
+        <v>76.38052350126654</v>
       </c>
       <c r="U11" t="n">
-        <v>24.43801426471705</v>
+        <v>24.29887064474913</v>
       </c>
       <c r="V11" t="n">
-        <v>181.8104673169108</v>
+        <v>181.461406656961</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75239745419699</v>
+        <v>1.702131016880436</v>
       </c>
       <c r="X11" t="n">
-        <v>78.51739375175907</v>
+        <v>78.17677465723131</v>
       </c>
       <c r="Y11" t="n">
-        <v>27403190.79854829</v>
+        <v>26755605.11073947</v>
       </c>
       <c r="Z11" t="n">
-        <v>82.04798320444606</v>
+        <v>81.91576904884761</v>
       </c>
     </row>
     <row r="12">
@@ -1385,76 +1385,76 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24.68215488215488</v>
+        <v>24.69458218549128</v>
       </c>
       <c r="D12" t="n">
-        <v>184.9391414141414</v>
+        <v>184.834435261708</v>
       </c>
       <c r="E12" t="n">
-        <v>2.213636363636363</v>
+        <v>2.216528925619834</v>
       </c>
       <c r="F12" t="n">
-        <v>79.82323232323232</v>
+        <v>79.80716253443525</v>
       </c>
       <c r="G12" t="n">
-        <v>29785223.06397307</v>
+        <v>29811152.43342516</v>
       </c>
       <c r="H12" t="n">
-        <v>84.46085858585859</v>
+        <v>84.48622589531681</v>
       </c>
       <c r="I12" t="n">
-        <v>26.41136363636364</v>
+        <v>26.40330578512397</v>
       </c>
       <c r="J12" t="n">
-        <v>182.0325757575758</v>
+        <v>181.9264462809917</v>
       </c>
       <c r="K12" t="n">
-        <v>3.124242424242424</v>
+        <v>3.108264462809917</v>
       </c>
       <c r="L12" t="n">
-        <v>85.33484848484848</v>
+        <v>85.27438016528926</v>
       </c>
       <c r="M12" t="n">
-        <v>73172727.27272727</v>
+        <v>72288429.75206612</v>
       </c>
       <c r="N12" t="n">
-        <v>87.56212121212121</v>
+        <v>87.5495867768595</v>
       </c>
       <c r="O12" t="n">
-        <v>24.36465025513938</v>
+        <v>24.19578007631368</v>
       </c>
       <c r="P12" t="n">
-        <v>184.0855234540017</v>
+        <v>184.1286518488099</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.862102128949955</v>
+        <v>1.814212423500961</v>
       </c>
       <c r="R12" t="n">
-        <v>75.34181815567685</v>
+        <v>74.94865010922322</v>
       </c>
       <c r="S12" t="n">
-        <v>19042710.4997961</v>
+        <v>18114850.84826241</v>
       </c>
       <c r="T12" t="n">
-        <v>81.57359960892569</v>
+        <v>81.41362381579773</v>
       </c>
       <c r="U12" t="n">
-        <v>24.7353765781675</v>
+        <v>24.8236193686961</v>
       </c>
       <c r="V12" t="n">
-        <v>178.3245861750497</v>
+        <v>178.5573025652949</v>
       </c>
       <c r="W12" t="n">
-        <v>2.272066858144224</v>
+        <v>2.29145261530172</v>
       </c>
       <c r="X12" t="n">
-        <v>80.33949292277298</v>
+        <v>80.48265538099298</v>
       </c>
       <c r="Y12" t="n">
-        <v>44759092.84970027</v>
+        <v>45657085.24780136</v>
       </c>
       <c r="Z12" t="n">
-        <v>85.03250932015318</v>
+        <v>85.09963583588903</v>
       </c>
     </row>
     <row r="13">
@@ -1473,22 +1473,22 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>24.82575757575757</v>
+        <v>24.73888888888889</v>
       </c>
       <c r="J13" t="n">
-        <v>184.276893939394</v>
+        <v>184.2055555555556</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>69.90568181818182</v>
+        <v>69.98333333333333</v>
       </c>
       <c r="M13" t="n">
-        <v>2496268.939393939</v>
+        <v>2580555.555555556</v>
       </c>
       <c r="N13" t="n">
-        <v>73.95719696969697</v>
+        <v>74.22777777777777</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1497,22 +1497,22 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>24.32956495098039</v>
+        <v>24.04481209150327</v>
       </c>
       <c r="V13" t="n">
-        <v>181.4938608776844</v>
+        <v>181.8084811702459</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>69.14041053921568</v>
+        <v>68.86662581699346</v>
       </c>
       <c r="Y13" t="n">
-        <v>2337370.046977124</v>
+        <v>2298258.101851852</v>
       </c>
       <c r="Z13" t="n">
-        <v>73.8545678688142</v>
+        <v>73.98942382508558</v>
       </c>
     </row>
     <row r="14">
@@ -1563,22 +1563,22 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>25.2375</v>
+        <v>25.25454545454545</v>
       </c>
       <c r="J15" t="n">
-        <v>180.3011363636364</v>
+        <v>180.4590909090909</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>70.11704545454546</v>
+        <v>70.07575757575758</v>
       </c>
       <c r="M15" t="n">
-        <v>2284943.181818182</v>
+        <v>2272954.545454545</v>
       </c>
       <c r="N15" t="n">
-        <v>72.90909090909091</v>
+        <v>72.93939393939394</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1587,22 +1587,22 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>22.64599726254138</v>
+        <v>22.77799635005517</v>
       </c>
       <c r="V15" t="n">
-        <v>179.6302048849843</v>
+        <v>179.1810139207198</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>66.54179929547577</v>
+        <v>66.56869535693066</v>
       </c>
       <c r="Y15" t="n">
-        <v>1682504.416539343</v>
+        <v>1690214.222052457</v>
       </c>
       <c r="Z15" t="n">
-        <v>74.4822542653425</v>
+        <v>74.46522790934556</v>
       </c>
     </row>
     <row r="16">
@@ -1679,76 +1679,76 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>23.40173611111111</v>
+        <v>23.49861111111111</v>
       </c>
       <c r="D18" t="n">
-        <v>181.2527777777778</v>
+        <v>181.262962962963</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>68.55381944444446</v>
+        <v>68.59027777777779</v>
       </c>
       <c r="G18" t="n">
-        <v>2099687.5</v>
+        <v>2073657.407407407</v>
       </c>
       <c r="H18" t="n">
-        <v>74.46041666666666</v>
+        <v>74.28055555555555</v>
       </c>
       <c r="I18" t="n">
-        <v>24.01972222222222</v>
+        <v>23.99965277777778</v>
       </c>
       <c r="J18" t="n">
-        <v>182.9066666666667</v>
+        <v>182.6833333333333</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>71.38555555555556</v>
+        <v>71.40694444444443</v>
       </c>
       <c r="M18" t="n">
-        <v>4284638.888888889</v>
+        <v>4308298.611111111</v>
       </c>
       <c r="N18" t="n">
-        <v>77.04472222222222</v>
+        <v>77.10590277777777</v>
       </c>
       <c r="O18" t="n">
-        <v>25.50162030521938</v>
+        <v>25.36234559214435</v>
       </c>
       <c r="P18" t="n">
-        <v>180.8198792156416</v>
+        <v>180.7385426578925</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>66.65396914746759</v>
+        <v>66.56918108551235</v>
       </c>
       <c r="S18" t="n">
-        <v>1495564.161350346</v>
+        <v>1526923.51143009</v>
       </c>
       <c r="T18" t="n">
-        <v>72.0411998970242</v>
+        <v>72.26419245529154</v>
       </c>
       <c r="U18" t="n">
-        <v>24.0197809865573</v>
+        <v>24.06044051891092</v>
       </c>
       <c r="V18" t="n">
-        <v>180.5749984587136</v>
+        <v>180.9409119389383</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>68.87206981357136</v>
+        <v>68.7712847459558</v>
       </c>
       <c r="Y18" t="n">
-        <v>2870247.557814992</v>
+        <v>2796514.804411597</v>
       </c>
       <c r="Z18" t="n">
-        <v>74.91416663316045</v>
+        <v>74.75720408976989</v>
       </c>
     </row>
     <row r="19">
@@ -1831,22 +1831,22 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>27.81944444444445</v>
+        <v>27.7</v>
       </c>
       <c r="J21" t="n">
-        <v>183.2555555555556</v>
+        <v>183.1166666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>1.177777777777778</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="L21" t="n">
-        <v>70.75416666666666</v>
+        <v>70.71666666666667</v>
       </c>
       <c r="M21" t="n">
-        <v>1853020.833333333</v>
+        <v>1868750</v>
       </c>
       <c r="N21" t="n">
-        <v>72.01666666666668</v>
+        <v>72.05</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -1855,22 +1855,22 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>25.89903721135844</v>
+        <v>26.03125216697871</v>
       </c>
       <c r="V21" t="n">
-        <v>180.8181548392969</v>
+        <v>180.8089751924277</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>67.70345687278969</v>
+        <v>67.48658683517094</v>
       </c>
       <c r="Y21" t="n">
-        <v>1508394.780723424</v>
+        <v>1462638.415765204</v>
       </c>
       <c r="Z21" t="n">
-        <v>71.64228631422924</v>
+        <v>71.40343119409195</v>
       </c>
     </row>
     <row r="22">
@@ -1883,22 +1883,22 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>26.31818181818182</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>183.0761363636364</v>
+        <v>183.0863636363636</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>70.01931818181818</v>
+        <v>69.85909090909091</v>
       </c>
       <c r="G22" t="n">
-        <v>2062954.545454546</v>
+        <v>2035454.545454546</v>
       </c>
       <c r="H22" t="n">
-        <v>72.26704545454545</v>
+        <v>72.12878787878788</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1907,22 +1907,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>24.16959586466165</v>
+        <v>23.81686856028961</v>
       </c>
       <c r="P22" t="n">
-        <v>182.5104845446951</v>
+        <v>182.7815719855194</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>65.26865601503761</v>
+        <v>64.25543024227234</v>
       </c>
       <c r="S22" t="n">
-        <v>1512135.442773601</v>
+        <v>1364388.923698134</v>
       </c>
       <c r="T22" t="n">
-        <v>70.8046888053467</v>
+        <v>70.32477025898079</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -1947,22 +1947,22 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>24.54545454545455</v>
+        <v>24.71212121212121</v>
       </c>
       <c r="J23" t="n">
-        <v>182.0454545454545</v>
+        <v>181.9242424242424</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>69.15909090909091</v>
+        <v>69.18181818181817</v>
       </c>
       <c r="M23" t="n">
-        <v>2135681.818181818</v>
+        <v>2096666.666666667</v>
       </c>
       <c r="N23" t="n">
-        <v>74.13636363636365</v>
+        <v>73.87878787878789</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -1971,22 +1971,22 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>26.41304563492064</v>
+        <v>26.47037037037038</v>
       </c>
       <c r="V23" t="n">
-        <v>179.4187003968254</v>
+        <v>179.0731481481481</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>67.79518849206349</v>
+        <v>67.92037037037038</v>
       </c>
       <c r="Y23" t="n">
-        <v>1484603.174603174</v>
+        <v>1508414.351851852</v>
       </c>
       <c r="Z23" t="n">
-        <v>70.92261904761905</v>
+        <v>71.0763888888889</v>
       </c>
     </row>
     <row r="24">
@@ -2101,22 +2101,22 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>27.53</v>
+        <v>27.4625</v>
       </c>
       <c r="J27" t="n">
-        <v>185.45</v>
+        <v>185.3625</v>
       </c>
       <c r="K27" t="n">
-        <v>1.03</v>
+        <v>1.0375</v>
       </c>
       <c r="L27" t="n">
-        <v>71.30999999999999</v>
+        <v>71.32499999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>2357000</v>
+        <v>2388750</v>
       </c>
       <c r="N27" t="n">
-        <v>72.74000000000001</v>
+        <v>72.825</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2125,22 +2125,22 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>28.01865942028985</v>
+        <v>28.03419384057971</v>
       </c>
       <c r="V27" t="n">
-        <v>184.3760869565217</v>
+        <v>184.3994565217391</v>
       </c>
       <c r="W27" t="n">
-        <v>1.082065217391304</v>
+        <v>1.080842391304348</v>
       </c>
       <c r="X27" t="n">
-        <v>70.66557971014493</v>
+        <v>70.72327898550725</v>
       </c>
       <c r="Y27" t="n">
-        <v>2244945.652173913</v>
+        <v>2269769.02173913</v>
       </c>
       <c r="Z27" t="n">
-        <v>72.43007246376813</v>
+        <v>72.45063405797102</v>
       </c>
     </row>
     <row r="28">
@@ -2185,22 +2185,22 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>24.03492063492064</v>
+        <v>24.10888888888889</v>
       </c>
       <c r="D29" t="n">
-        <v>182.6269841269841</v>
+        <v>182.66</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>67.4063492063492</v>
+        <v>67.50888888888889</v>
       </c>
       <c r="G29" t="n">
-        <v>1687261.904761905</v>
+        <v>1695611.111111111</v>
       </c>
       <c r="H29" t="n">
-        <v>73.78412698412697</v>
+        <v>73.64</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2209,22 +2209,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>23.9511485042735</v>
+        <v>24.10917022792023</v>
       </c>
       <c r="P29" t="n">
-        <v>182.9341212606838</v>
+        <v>182.8795227920228</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>66.13111645299145</v>
+        <v>66.19565527065527</v>
       </c>
       <c r="S29" t="n">
-        <v>1412748.063568376</v>
+        <v>1400157.14031339</v>
       </c>
       <c r="T29" t="n">
-        <v>72.81940438034188</v>
+        <v>72.78003917378918</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2307,22 +2307,22 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>26.15444444444444</v>
+        <v>26.26805555555556</v>
       </c>
       <c r="D32" t="n">
-        <v>182.4055555555555</v>
+        <v>182.5819444444444</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>72.10222222222221</v>
+        <v>72.20277777777778</v>
       </c>
       <c r="G32" t="n">
-        <v>3227888.888888889</v>
+        <v>3249861.111111111</v>
       </c>
       <c r="H32" t="n">
-        <v>74.70555555555555</v>
+        <v>74.73194444444445</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2331,22 +2331,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>25.41227404309246</v>
+        <v>25.37563667151263</v>
       </c>
       <c r="P32" t="n">
-        <v>183.9471014918585</v>
+        <v>183.9485827471761</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>68.78982615849624</v>
+        <v>68.68581210988501</v>
       </c>
       <c r="S32" t="n">
-        <v>2329014.947967634</v>
+        <v>2330055.449665424</v>
       </c>
       <c r="T32" t="n">
-        <v>73.52862444460911</v>
+        <v>73.41813349693786</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -2403,22 +2403,22 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>25.575</v>
+        <v>25.21666666666667</v>
       </c>
       <c r="J34" t="n">
-        <v>180.2625</v>
+        <v>180.25</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>69.9375</v>
+        <v>69.78333333333333</v>
       </c>
       <c r="M34" t="n">
-        <v>2551875</v>
+        <v>2562500</v>
       </c>
       <c r="N34" t="n">
-        <v>73.47499999999999</v>
+        <v>73.76666666666667</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -2427,22 +2427,22 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>24.87872023809524</v>
+        <v>25.18154761904762</v>
       </c>
       <c r="V34" t="n">
-        <v>178.8340773809524</v>
+        <v>179.014880952381</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>67.6547619047619</v>
+        <v>67.8938492063492</v>
       </c>
       <c r="Y34" t="n">
-        <v>1660279.017857143</v>
+        <v>1700659.722222222</v>
       </c>
       <c r="Z34" t="n">
-        <v>73.7202380952381</v>
+        <v>73.625</v>
       </c>
     </row>
     <row r="35">
@@ -2455,76 +2455,76 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>26.73827160493827</v>
+        <v>26.75277777777778</v>
       </c>
       <c r="D35" t="n">
-        <v>184.3731481481481</v>
+        <v>184.5333333333333</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>69.69259259259259</v>
+        <v>69.76547619047618</v>
       </c>
       <c r="G35" t="n">
-        <v>1850740.740740741</v>
+        <v>1856755.952380953</v>
       </c>
       <c r="H35" t="n">
-        <v>71.66697530864197</v>
+        <v>71.64325396825397</v>
       </c>
       <c r="I35" t="n">
-        <v>22.08194444444445</v>
+        <v>22.13148148148148</v>
       </c>
       <c r="J35" t="n">
-        <v>182.2559027777778</v>
+        <v>182.6263888888889</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>69.44027777777778</v>
+        <v>69.42777777777778</v>
       </c>
       <c r="M35" t="n">
-        <v>3137951.388888889</v>
+        <v>3138009.259259259</v>
       </c>
       <c r="N35" t="n">
-        <v>77.55694444444444</v>
+        <v>77.55740740740741</v>
       </c>
       <c r="O35" t="n">
-        <v>23.42063563467072</v>
+        <v>23.70000091804603</v>
       </c>
       <c r="P35" t="n">
-        <v>181.9241344100993</v>
+        <v>181.826948323189</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>66.54489857121436</v>
+        <v>66.86725054394228</v>
       </c>
       <c r="S35" t="n">
-        <v>1645896.882519689</v>
+        <v>1690302.794532118</v>
       </c>
       <c r="T35" t="n">
-        <v>73.33589029553943</v>
+        <v>73.30192697861871</v>
       </c>
       <c r="U35" t="n">
-        <v>22.40219417429443</v>
+        <v>22.48348112128146</v>
       </c>
       <c r="V35" t="n">
-        <v>181.3653292137793</v>
+        <v>181.5315500628169</v>
       </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>66.24453065408085</v>
+        <v>66.44548531655225</v>
       </c>
       <c r="Y35" t="n">
-        <v>1755605.417045251</v>
+        <v>1820668.333838112</v>
       </c>
       <c r="Z35" t="n">
-        <v>73.74275067864674</v>
+        <v>73.84311201597343</v>
       </c>
     </row>
     <row r="36">
@@ -2537,22 +2537,22 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>26.7375</v>
+        <v>26.85</v>
       </c>
       <c r="D36" t="n">
-        <v>181.825</v>
+        <v>181.4666666666667</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>66.825</v>
+        <v>66.85000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>1085937.5</v>
+        <v>1078333.333333333</v>
       </c>
       <c r="H36" t="n">
-        <v>69.32499999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -2561,22 +2561,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>27.49273125449112</v>
+        <v>27.19016403917719</v>
       </c>
       <c r="P36" t="n">
-        <v>182.0877166966805</v>
+        <v>182.4221504007688</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>65.55685345356397</v>
+        <v>65.50509753404491</v>
       </c>
       <c r="S36" t="n">
-        <v>871766.9741168919</v>
+        <v>896852.7187359425</v>
       </c>
       <c r="T36" t="n">
-        <v>68.23378406133341</v>
+        <v>68.52780154786733</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
@@ -2659,22 +2659,22 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>24.69642857142857</v>
+        <v>24.625</v>
       </c>
       <c r="D39" t="n">
-        <v>179.9642857142857</v>
+        <v>180.0625</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>68.98214285714286</v>
+        <v>69.02083333333333</v>
       </c>
       <c r="G39" t="n">
-        <v>1917857.142857143</v>
+        <v>1941666.666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>73.78571428571429</v>
+        <v>73.95833333333333</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -2683,22 +2683,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>24.66104906875031</v>
+        <v>24.19036561993218</v>
       </c>
       <c r="P39" t="n">
-        <v>179.4951541621433</v>
+        <v>180.210887810733</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>67.50847260754381</v>
+        <v>67.20232994845998</v>
       </c>
       <c r="S39" t="n">
-        <v>1584282.536778667</v>
+        <v>1572038.021747774</v>
       </c>
       <c r="T39" t="n">
-        <v>72.88109003569531</v>
+        <v>72.99934811776917</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
@@ -2781,22 +2781,22 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>24.19545454545455</v>
+        <v>24.19393939393939</v>
       </c>
       <c r="D42" t="n">
-        <v>183.3590909090909</v>
+        <v>183.3954545454546</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>69.87613636363636</v>
+        <v>69.81818181818183</v>
       </c>
       <c r="G42" t="n">
-        <v>2527954.545454545</v>
+        <v>2493939.393939394</v>
       </c>
       <c r="H42" t="n">
-        <v>74.09090909090909</v>
+        <v>74.10454545454546</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -2805,22 +2805,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>24.049227915804</v>
+        <v>23.89619277662755</v>
       </c>
       <c r="P42" t="n">
-        <v>182.4102462905452</v>
+        <v>182.3442172762825</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>68.46791105935128</v>
+        <v>68.31554807913504</v>
       </c>
       <c r="S42" t="n">
-        <v>2306720.637077295</v>
+        <v>2277340.479066023</v>
       </c>
       <c r="T42" t="n">
-        <v>74.24992236024845</v>
+        <v>74.16471129514608</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -2871,22 +2871,22 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>24.03818181818182</v>
+        <v>23.98686868686869</v>
       </c>
       <c r="D44" t="n">
-        <v>182.3655808080808</v>
+        <v>182.3089786756453</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>71.67818181818181</v>
+        <v>71.58686868686868</v>
       </c>
       <c r="G44" t="n">
-        <v>4148545.454545455</v>
+        <v>4096994.94949495</v>
       </c>
       <c r="H44" t="n">
-        <v>77.17017676767678</v>
+        <v>77.17519640852976</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -2895,22 +2895,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>23.23972415011889</v>
+        <v>23.14731254775115</v>
       </c>
       <c r="P44" t="n">
-        <v>180.0264973330763</v>
+        <v>179.8548383065927</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>69.24250851487693</v>
+        <v>69.22183485779978</v>
       </c>
       <c r="S44" t="n">
-        <v>2863183.678346507</v>
+        <v>2913259.64260723</v>
       </c>
       <c r="T44" t="n">
-        <v>76.43462799627272</v>
+        <v>76.40355491649352</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
@@ -2929,76 +2929,76 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>24.2050505050505</v>
+        <v>24.14935064935065</v>
       </c>
       <c r="D45" t="n">
-        <v>179.6383838383839</v>
+        <v>179.7064935064935</v>
       </c>
       <c r="E45" t="n">
-        <v>1.093939393939394</v>
+        <v>1.092207792207792</v>
       </c>
       <c r="F45" t="n">
-        <v>70.02121212121213</v>
+        <v>69.84155844155845</v>
       </c>
       <c r="G45" t="n">
-        <v>3147020.202020202</v>
+        <v>3043311.688311689</v>
       </c>
       <c r="H45" t="n">
-        <v>75.11414141414143</v>
+        <v>75.03246753246754</v>
       </c>
       <c r="I45" t="n">
-        <v>26.69772727272727</v>
+        <v>27.11212121212121</v>
       </c>
       <c r="J45" t="n">
-        <v>183.0136363636364</v>
+        <v>182.8666666666667</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>67.42500000000001</v>
+        <v>67.71818181818183</v>
       </c>
       <c r="M45" t="n">
-        <v>1249943.181818182</v>
+        <v>1266969.696969697</v>
       </c>
       <c r="N45" t="n">
-        <v>70.65454545454546</v>
+        <v>70.53939393939393</v>
       </c>
       <c r="O45" t="n">
-        <v>25.63840771413235</v>
+        <v>25.68600599660154</v>
       </c>
       <c r="P45" t="n">
-        <v>180.4452573783137</v>
+        <v>180.6379499625938</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.021552050772</v>
+        <v>1.021757398611619</v>
       </c>
       <c r="R45" t="n">
-        <v>70.2869620472988</v>
+        <v>70.42952543336175</v>
       </c>
       <c r="S45" t="n">
-        <v>3089030.458801878</v>
+        <v>3078919.763557597</v>
       </c>
       <c r="T45" t="n">
-        <v>74.53751178410172</v>
+        <v>74.57694092129604</v>
       </c>
       <c r="U45" t="n">
-        <v>25.72169384057971</v>
+        <v>25.6219806763285</v>
       </c>
       <c r="V45" t="n">
-        <v>184.5289855072464</v>
+        <v>184.8303140096618</v>
       </c>
       <c r="W45" t="n">
-        <v>1.015625</v>
+        <v>1.006944444444444</v>
       </c>
       <c r="X45" t="n">
-        <v>66.62839673913044</v>
+        <v>66.38647342995169</v>
       </c>
       <c r="Y45" t="n">
-        <v>1802179.574275362</v>
+        <v>1427906.099033816</v>
       </c>
       <c r="Z45" t="n">
-        <v>70.3629981884058</v>
+        <v>70.14371980676329</v>
       </c>
     </row>
     <row r="46">
@@ -3011,22 +3011,22 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>24.02272727272727</v>
+        <v>24.42424242424243</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2386363636364</v>
+        <v>181.1666666666667</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>67.97727272727272</v>
+        <v>68.2878787878788</v>
       </c>
       <c r="G46" t="n">
-        <v>2198011.363636364</v>
+        <v>2233333.333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>74.15909090909091</v>
+        <v>73.81818181818183</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -3035,22 +3035,22 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>24.72708333333333</v>
+        <v>24.5765873015873</v>
       </c>
       <c r="P46" t="n">
-        <v>180.9827704451346</v>
+        <v>181.5345669427191</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>66.45497541407867</v>
+        <v>66.51139579020014</v>
       </c>
       <c r="S46" t="n">
-        <v>1385517.436594203</v>
+        <v>1416180.986887509</v>
       </c>
       <c r="T46" t="n">
-        <v>72.04039208074533</v>
+        <v>72.20861801242236</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
@@ -3069,76 +3069,76 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>23.15876951331497</v>
+        <v>23.00516273849607</v>
       </c>
       <c r="D47" t="n">
-        <v>184.1435261707989</v>
+        <v>184.3420875420876</v>
       </c>
       <c r="E47" t="n">
-        <v>1.240495867768595</v>
+        <v>1.238383838383838</v>
       </c>
       <c r="F47" t="n">
-        <v>74.33544536271808</v>
+        <v>74.33221099887766</v>
       </c>
       <c r="G47" t="n">
-        <v>8546896.235078054</v>
+        <v>8636206.509539843</v>
       </c>
       <c r="H47" t="n">
-        <v>80.26988062442609</v>
+        <v>80.46318742985412</v>
       </c>
       <c r="I47" t="n">
-        <v>24.275</v>
+        <v>24.06666666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>181.825</v>
+        <v>181.95</v>
       </c>
       <c r="K47" t="n">
-        <v>1.0875</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="L47" t="n">
-        <v>69.92500000000001</v>
+        <v>69.68333333333334</v>
       </c>
       <c r="M47" t="n">
-        <v>2531250</v>
+        <v>2498333.333333333</v>
       </c>
       <c r="N47" t="n">
-        <v>75.6375</v>
+        <v>75.71666666666667</v>
       </c>
       <c r="O47" t="n">
-        <v>24.74341362541827</v>
+        <v>24.83222776440011</v>
       </c>
       <c r="P47" t="n">
-        <v>180.7574865193286</v>
+        <v>180.4883168569572</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.06757116722287</v>
+        <v>1.054809204383508</v>
       </c>
       <c r="R47" t="n">
-        <v>73.15568706749046</v>
+        <v>73.2736175269328</v>
       </c>
       <c r="S47" t="n">
-        <v>5394640.210151047</v>
+        <v>5469143.590184612</v>
       </c>
       <c r="T47" t="n">
-        <v>77.28504103395744</v>
+        <v>77.28588348594798</v>
       </c>
       <c r="U47" t="n">
-        <v>22.20630281633571</v>
+        <v>22.26025560696614</v>
       </c>
       <c r="V47" t="n">
-        <v>179.3947324240087</v>
+        <v>179.6226061949746</v>
       </c>
       <c r="W47" t="n">
-        <v>1.006578947368421</v>
+        <v>1.008771929824561</v>
       </c>
       <c r="X47" t="n">
-        <v>65.82074195906434</v>
+        <v>65.94247076023392</v>
       </c>
       <c r="Y47" t="n">
-        <v>1884488.945721676</v>
+        <v>1891559.335036309</v>
       </c>
       <c r="Z47" t="n">
-        <v>74.07281665702718</v>
+        <v>74.26931109825847</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/england/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -729,22 +729,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>24.43055555555556</v>
+        <v>24.421875</v>
       </c>
       <c r="D4" t="n">
-        <v>182.8194444444445</v>
+        <v>183.015625</v>
       </c>
       <c r="E4" t="n">
-        <v>2.237654320987654</v>
+        <v>2.267361111111111</v>
       </c>
       <c r="F4" t="n">
-        <v>83.39969135802468</v>
+        <v>83.63715277777777</v>
       </c>
       <c r="G4" t="n">
-        <v>58353395.0617284</v>
+        <v>60272569.44444445</v>
       </c>
       <c r="H4" t="n">
-        <v>86.29320987654322</v>
+        <v>86.47048611111111</v>
       </c>
       <c r="I4" t="n">
         <v>26.30208333333333</v>
@@ -765,22 +765,22 @@
         <v>79.60243055555556</v>
       </c>
       <c r="O4" t="n">
-        <v>24.62855154821099</v>
+        <v>24.61337049173736</v>
       </c>
       <c r="P4" t="n">
-        <v>179.6639443975357</v>
+        <v>179.3531874472277</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.786677478008747</v>
+        <v>1.778762162759841</v>
       </c>
       <c r="R4" t="n">
-        <v>81.20959484272177</v>
+        <v>81.167044198062</v>
       </c>
       <c r="S4" t="n">
-        <v>37511264.34624887</v>
+        <v>37184547.38952997</v>
       </c>
       <c r="T4" t="n">
-        <v>84.5578965238408</v>
+        <v>84.52763358932089</v>
       </c>
       <c r="U4" t="n">
         <v>24.26935235816815</v>
@@ -829,22 +829,22 @@
         <v>79.11363636363636</v>
       </c>
       <c r="I5" t="n">
-        <v>25.67184343434343</v>
+        <v>25.68845598845598</v>
       </c>
       <c r="J5" t="n">
-        <v>182.0694444444445</v>
+        <v>182.015873015873</v>
       </c>
       <c r="K5" t="n">
-        <v>1.377146464646464</v>
+        <v>1.367532467532467</v>
       </c>
       <c r="L5" t="n">
-        <v>75.41047979797979</v>
+        <v>75.45324675324675</v>
       </c>
       <c r="M5" t="n">
-        <v>9254898.989898989</v>
+        <v>9313535.353535352</v>
       </c>
       <c r="N5" t="n">
-        <v>80.11426767676768</v>
+        <v>80.05122655122656</v>
       </c>
       <c r="O5" t="n">
         <v>24.87299735111436</v>
@@ -865,22 +865,22 @@
         <v>77.10427627572768</v>
       </c>
       <c r="U5" t="n">
-        <v>23.43655318852687</v>
+        <v>23.25428023182958</v>
       </c>
       <c r="V5" t="n">
-        <v>177.9099450013924</v>
+        <v>177.9513197055138</v>
       </c>
       <c r="W5" t="n">
-        <v>1.406175160122529</v>
+        <v>1.42405231829574</v>
       </c>
       <c r="X5" t="n">
-        <v>73.04707254246728</v>
+        <v>73.02006187343358</v>
       </c>
       <c r="Y5" t="n">
-        <v>8271997.006404902</v>
+        <v>8502707.158521302</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.20906780840993</v>
+        <v>80.41941181077695</v>
       </c>
     </row>
     <row r="6">
@@ -1075,22 +1075,22 @@
         <v>80.47532467532469</v>
       </c>
       <c r="I8" t="n">
-        <v>26.17045454545455</v>
+        <v>26.33766233766234</v>
       </c>
       <c r="J8" t="n">
-        <v>182.5</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="K8" t="n">
-        <v>2.113636363636364</v>
+        <v>2.168831168831169</v>
       </c>
       <c r="L8" t="n">
-        <v>79.60227272727272</v>
+        <v>80.05194805194806</v>
       </c>
       <c r="M8" t="n">
-        <v>25338636.36363636</v>
+        <v>26540259.74025974</v>
       </c>
       <c r="N8" t="n">
-        <v>81.59090909090909</v>
+        <v>81.77922077922078</v>
       </c>
       <c r="O8" t="n">
         <v>27.20553130343046</v>
@@ -1111,22 +1111,22 @@
         <v>77.50941649387028</v>
       </c>
       <c r="U8" t="n">
-        <v>23.48214869281045</v>
+        <v>23.50816993464052</v>
       </c>
       <c r="V8" t="n">
-        <v>183.3155535130719</v>
+        <v>183.4534897292251</v>
       </c>
       <c r="W8" t="n">
-        <v>1.711815767973856</v>
+        <v>1.684932306255835</v>
       </c>
       <c r="X8" t="n">
-        <v>73.77625612745098</v>
+        <v>73.68714985994397</v>
       </c>
       <c r="Y8" t="n">
-        <v>14425370.45547386</v>
+        <v>13882030.52054155</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.41954656862745</v>
+        <v>79.36519607843138</v>
       </c>
     </row>
     <row r="9">
@@ -1139,22 +1139,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.95568181818182</v>
+        <v>25.93506493506494</v>
       </c>
       <c r="D9" t="n">
-        <v>184.4272727272727</v>
+        <v>184.2597402597403</v>
       </c>
       <c r="E9" t="n">
-        <v>1.056818181818182</v>
+        <v>1.064935064935065</v>
       </c>
       <c r="F9" t="n">
-        <v>76.55454545454546</v>
+        <v>76.66233766233766</v>
       </c>
       <c r="G9" t="n">
-        <v>11720000</v>
+        <v>11971428.57142857</v>
       </c>
       <c r="H9" t="n">
-        <v>79.12045454545455</v>
+        <v>79.1948051948052</v>
       </c>
       <c r="I9" t="n">
         <v>25.53409090909091</v>
@@ -1175,22 +1175,22 @@
         <v>80.13636363636363</v>
       </c>
       <c r="O9" t="n">
-        <v>24.86640651874785</v>
+        <v>24.93975871050174</v>
       </c>
       <c r="P9" t="n">
-        <v>180.4564907980736</v>
+        <v>180.8494348616639</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.095274337805298</v>
+        <v>1.083674873458155</v>
       </c>
       <c r="R9" t="n">
-        <v>73.88460182318542</v>
+        <v>73.79248611725393</v>
       </c>
       <c r="S9" t="n">
-        <v>7821598.619711042</v>
+        <v>7413969.851098334</v>
       </c>
       <c r="T9" t="n">
-        <v>77.71509932920537</v>
+        <v>77.66599587203302</v>
       </c>
       <c r="U9" t="n">
         <v>26.62493530020704</v>
@@ -1239,22 +1239,22 @@
         <v>83.33232323232323</v>
       </c>
       <c r="I10" t="n">
-        <v>26.40330578512397</v>
+        <v>26.57999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>181.9264462809917</v>
+        <v>182.2009090909091</v>
       </c>
       <c r="K10" t="n">
-        <v>3.108264462809917</v>
+        <v>3.155454545454545</v>
       </c>
       <c r="L10" t="n">
-        <v>85.27438016528926</v>
+        <v>85.45636363636365</v>
       </c>
       <c r="M10" t="n">
-        <v>72288429.75206612</v>
+        <v>73403636.36363636</v>
       </c>
       <c r="N10" t="n">
-        <v>87.5495867768595</v>
+        <v>87.62272727272727</v>
       </c>
       <c r="O10" t="n">
         <v>23.1324725968077</v>
@@ -1275,22 +1275,22 @@
         <v>81.27796518749969</v>
       </c>
       <c r="U10" t="n">
-        <v>24.8236193686961</v>
+        <v>24.83455273413713</v>
       </c>
       <c r="V10" t="n">
-        <v>178.5573025652949</v>
+        <v>178.5558899646815</v>
       </c>
       <c r="W10" t="n">
-        <v>2.29145261530172</v>
+        <v>2.306312162546178</v>
       </c>
       <c r="X10" t="n">
-        <v>80.48265538099298</v>
+        <v>80.69758758575895</v>
       </c>
       <c r="Y10" t="n">
-        <v>45657085.24780136</v>
+        <v>45936698.53448626</v>
       </c>
       <c r="Z10" t="n">
-        <v>85.09963583588903</v>
+        <v>85.20007560995411</v>
       </c>
     </row>
     <row r="11">
@@ -1403,22 +1403,22 @@
         <v>84.48622589531681</v>
       </c>
       <c r="I12" t="n">
-        <v>26.40330578512397</v>
+        <v>26.57999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>181.9264462809917</v>
+        <v>182.2009090909091</v>
       </c>
       <c r="K12" t="n">
-        <v>3.108264462809917</v>
+        <v>3.155454545454545</v>
       </c>
       <c r="L12" t="n">
-        <v>85.27438016528926</v>
+        <v>85.45636363636365</v>
       </c>
       <c r="M12" t="n">
-        <v>72288429.75206612</v>
+        <v>73403636.36363636</v>
       </c>
       <c r="N12" t="n">
-        <v>87.5495867768595</v>
+        <v>87.62272727272727</v>
       </c>
       <c r="O12" t="n">
         <v>24.19578007631368</v>
@@ -1439,22 +1439,22 @@
         <v>81.41362381579773</v>
       </c>
       <c r="U12" t="n">
-        <v>24.8236193686961</v>
+        <v>24.83455273413713</v>
       </c>
       <c r="V12" t="n">
-        <v>178.5573025652949</v>
+        <v>178.5558899646815</v>
       </c>
       <c r="W12" t="n">
-        <v>2.29145261530172</v>
+        <v>2.306312162546178</v>
       </c>
       <c r="X12" t="n">
-        <v>80.48265538099298</v>
+        <v>80.69758758575895</v>
       </c>
       <c r="Y12" t="n">
-        <v>45657085.24780136</v>
+        <v>45936698.53448626</v>
       </c>
       <c r="Z12" t="n">
-        <v>85.09963583588903</v>
+        <v>85.20007560995411</v>
       </c>
     </row>
     <row r="13">
